--- a/src/R/translations.xlsx
+++ b/src/R/translations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5aee5c5b004427f/Documents/mr-risk-assessment/src/R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{4649215D-82E5-4B27-B6A2-F5C81FA3C8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC46462B-165B-4FAF-858F-A03536C628BE}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{132F1232-AAEB-42DF-9114-B0462C5F7248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{278938BD-8EEF-4A72-B5CF-EA4A40E5C537}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{41A3C097-9B5C-484B-88DA-6A6C7D19F152}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{41A3C097-9B5C-484B-88DA-6A6C7D19F152}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="MSG" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DASHBOARD!$A$1:$E$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DASHBOARD!$A$1:$E$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MSG!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">QA_REPORT!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">REPORT!$A$1:$E$170</definedName>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2285" uniqueCount="1672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2310" uniqueCount="1681">
   <si>
     <t>LABEL</t>
   </si>
@@ -7245,78 +7245,24 @@
     <t>Fechar</t>
   </si>
   <si>
-    <t>silent_mun_lab</t>
-  </si>
-  <si>
-    <t>Municipios silenciosos</t>
-  </si>
-  <si>
-    <t>Silent municipalities</t>
-  </si>
-  <si>
-    <t>Municípios silenciosos</t>
-  </si>
-  <si>
-    <t>Municipalités silencieuses</t>
-  </si>
-  <si>
-    <t>silent_mun_legend</t>
-  </si>
-  <si>
     <t>Reporta casos sospechosos</t>
   </si>
   <si>
     <t>Signale des cas suspects</t>
   </si>
   <si>
-    <t>silent_mun_infobox_text</t>
-  </si>
-  <si>
     <t>title_figure_3f</t>
   </si>
   <si>
-    <t>silent_mun_lab_pct</t>
-  </si>
-  <si>
-    <t>Notifica casos suspeitos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reports suspected cases </t>
-  </si>
-  <si>
     <t>Equipo capacitado en los últimos 2 años</t>
   </si>
   <si>
     <t>Areas subnacionales con un equipo que ha sido capacitado en respuesta a brotes en los últimos 2 años</t>
   </si>
   <si>
-    <t>Municipios que no reportan casos sospechosos</t>
-  </si>
-  <si>
-    <t>Número de municipios que no reportan casos sospechosos</t>
-  </si>
-  <si>
     <t>Presencia de un equipo capacitado en los últimos 2 años (Puntaje)</t>
   </si>
   <si>
-    <t>Municipalities that do not report suspected cases</t>
-  </si>
-  <si>
-    <t>Number of municipalities that do not report suspected cases</t>
-  </si>
-  <si>
-    <t>Municípios que não reportam casos suspeitos</t>
-  </si>
-  <si>
-    <t>Número de municípios que não reportam casos suspeitos</t>
-  </si>
-  <si>
-    <t>Municipalités qui ne signalent pas de cas suspects</t>
-  </si>
-  <si>
-    <t>Nombre de municipalités qui ne signalent pas de cas suspects</t>
-  </si>
-  <si>
     <t>Trained team in the last 2 years</t>
   </si>
   <si>
@@ -7344,18 +7290,6 @@
     <t>Présence d'une équipe formée au cours des 2 dernières années (Score)</t>
   </si>
   <si>
-    <t>Porcentaje de municipios que no reportan casos sospechosos</t>
-  </si>
-  <si>
-    <t>Percentage of municipalities that do not report suspected cases</t>
-  </si>
-  <si>
-    <t>Proporção de municípios que não reportam casos suspeitos</t>
-  </si>
-  <si>
-    <t>Proportion de municipalités qui ne signalent pas de cas suspects</t>
-  </si>
-  <si>
     <t>Presencia de un equipo capacitado en los últimos 2 años</t>
   </si>
   <si>
@@ -7369,6 +7303,99 @@
   </si>
   <si>
     <t>Áreas subnacionais (estadual) com uma equipe que foi treinada para resposta a surtos nos últimos 2 anos</t>
+  </si>
+  <si>
+    <t>case_class_lab</t>
+  </si>
+  <si>
+    <t>Distribución espacial de municipios notificando casos de sarampión y rubeola</t>
+  </si>
+  <si>
+    <t>Número de municipios que reportan casos</t>
+  </si>
+  <si>
+    <t>case_class_infobox_text</t>
+  </si>
+  <si>
+    <t>case_class_legend_rep</t>
+  </si>
+  <si>
+    <t>case_class_legend_conf</t>
+  </si>
+  <si>
+    <t>Reporta casos confirmados</t>
+  </si>
+  <si>
+    <t>Número de municipios que reportan casos confirmados</t>
+  </si>
+  <si>
+    <t>case_class_lab_short</t>
+  </si>
+  <si>
+    <t>Casos reportados</t>
+  </si>
+  <si>
+    <t>Spatial distribution of municipalities reporting measles and rubella cases</t>
+  </si>
+  <si>
+    <t>Distribuição espacial dos municípios notificando casos de sarampo e rubéola</t>
+  </si>
+  <si>
+    <t>Distribution spatiale des municipalités signalant des cas de rougeole et de rubéole</t>
+  </si>
+  <si>
+    <t>Reports suspected cases</t>
+  </si>
+  <si>
+    <t>Reporta casos suspeitos</t>
+  </si>
+  <si>
+    <t>Number of municipalities reporting confirmed cases</t>
+  </si>
+  <si>
+    <t>Número de municípios que reportam casos confirmados</t>
+  </si>
+  <si>
+    <t>Nombre de municipalités signalant des cas confirmés</t>
+  </si>
+  <si>
+    <t>Reports confirmed cases</t>
+  </si>
+  <si>
+    <t>Signale des cas confirmés</t>
+  </si>
+  <si>
+    <t>Reported cases</t>
+  </si>
+  <si>
+    <t>Cas signalés</t>
+  </si>
+  <si>
+    <t>case_class_infobox_pct</t>
+  </si>
+  <si>
+    <t>Porcentaje de municipios que reportan casos confirmados</t>
+  </si>
+  <si>
+    <t>Percentage of municipalities reporting confirmed cases</t>
+  </si>
+  <si>
+    <t>Percentual de municípios que reportam casos confirmados</t>
+  </si>
+  <si>
+    <t>Pourcentage de municipalités signalant des cas confirmés</t>
+  </si>
+  <si>
+    <t>surv_table_cases_conf</t>
+  </si>
+  <si>
+    <t>Casos confirmados</t>
+  </si>
+  <si>
+    <t>Confirmed cases</t>
+  </si>
+  <si>
+    <t>Cas confirmés</t>
   </si>
 </sst>
 </file>
@@ -7927,7 +7954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064C7D9D-C4E2-B94C-B003-B8DCE10597B7}">
-  <dimension ref="A1:E174"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
@@ -8938,21 +8965,21 @@
         <v>976</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C60" s="15" t="s">
         <v>1632</v>
       </c>
+      <c r="B60" s="9" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>1660</v>
+      </c>
       <c r="D60" s="3" t="s">
-        <v>1633</v>
+        <v>1661</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>1634</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
@@ -9232,16 +9259,16 @@
         <v>211</v>
       </c>
       <c r="B77" t="s">
-        <v>1644</v>
+        <v>1634</v>
       </c>
       <c r="C77" t="s">
-        <v>1655</v>
+        <v>1637</v>
       </c>
       <c r="D77" t="s">
-        <v>1671</v>
+        <v>1649</v>
       </c>
       <c r="E77" t="s">
-        <v>1661</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
@@ -10728,16 +10755,16 @@
         <v>421</v>
       </c>
       <c r="B165" t="s">
-        <v>1644</v>
+        <v>1634</v>
       </c>
       <c r="C165" t="s">
-        <v>1655</v>
+        <v>1637</v>
       </c>
       <c r="D165" t="s">
-        <v>1658</v>
+        <v>1640</v>
       </c>
       <c r="E165" t="s">
-        <v>1661</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
@@ -10779,16 +10806,16 @@
         <v>425</v>
       </c>
       <c r="B168" t="s">
-        <v>1667</v>
+        <v>1645</v>
       </c>
       <c r="C168" t="s">
-        <v>1668</v>
+        <v>1646</v>
       </c>
       <c r="D168" t="s">
-        <v>1669</v>
+        <v>1647</v>
       </c>
       <c r="E168" t="s">
-        <v>1670</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
@@ -10825,72 +10852,106 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
-        <v>1630</v>
+        <v>1650</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>1648</v>
-      </c>
-      <c r="D171" s="7" t="s">
-        <v>1650</v>
-      </c>
-      <c r="E171" s="7" t="s">
-        <v>1652</v>
+        <v>1651</v>
+      </c>
+      <c r="C171" s="9" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>1662</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
-        <v>1635</v>
+        <v>1654</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>1636</v>
-      </c>
-      <c r="C172" s="8" t="s">
-        <v>1642</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>1641</v>
-      </c>
-      <c r="E172" s="7" t="s">
-        <v>1637</v>
+        <v>1630</v>
+      </c>
+      <c r="C172" s="9" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D172" s="9" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>1631</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
-        <v>1638</v>
+        <v>1653</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>1646</v>
-      </c>
-      <c r="C173" s="7" t="s">
-        <v>1649</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>1651</v>
-      </c>
-      <c r="E173" s="7" t="s">
-        <v>1653</v>
+        <v>1657</v>
+      </c>
+      <c r="C173" s="9" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>1667</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
-        <v>1640</v>
+        <v>1655</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C174" s="7" t="s">
-        <v>1664</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>1665</v>
-      </c>
-      <c r="E174" s="7" t="s">
-        <v>1666</v>
+        <v>1656</v>
+      </c>
+      <c r="C174" s="9" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D174" s="9" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E174" s="9" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A175" s="7" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A176" s="7" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C176" s="9" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>1676</v>
       </c>
     </row>
   </sheetData>
@@ -12161,7 +12222,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01EA010-864B-8746-BF5D-2E469295667F}">
-  <dimension ref="A1:E198"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.5" bestFit="1" customWidth="1"/>
@@ -14109,738 +14170,738 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>728</v>
+        <v>1677</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>729</v>
+        <v>1678</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>1245</v>
+        <v>1679</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>1585</v>
+        <v>1678</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>1433</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
+        <v>728</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="C116" s="15" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
         <v>730</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B117" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="C116" s="15" t="s">
+      <c r="C117" s="15" t="s">
         <v>1246</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D117" s="3" t="s">
         <v>1586</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="E117" s="3" t="s">
         <v>1434</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+    <row r="118" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
         <v>732</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B118" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="C117" s="15" t="s">
+      <c r="C118" s="15" t="s">
         <v>1247</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D118" s="3" t="s">
         <v>1587</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E118" s="3" t="s">
         <v>1435</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>734</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="C118" s="15" t="s">
-        <v>1248</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>1588</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="C119" s="13" t="s">
-        <v>738</v>
+        <v>735</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>1248</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>739</v>
+        <v>1588</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="C120" s="15" t="s">
-        <v>1249</v>
+        <v>737</v>
+      </c>
+      <c r="C120" s="13" t="s">
+        <v>738</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>1589</v>
+        <v>739</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
+        <v>740</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="C121" s="15" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>742</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B122" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C122" s="13" t="s">
         <v>1250</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D122" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E122" s="3" t="s">
         <v>1439</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>745</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="C122" s="15" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
+        <v>747</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
         <v>749</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B125" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="C124" s="15" t="s">
+      <c r="C125" s="15" t="s">
         <v>1253</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="D125" s="3" t="s">
         <v>1592</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="E125" s="3" t="s">
         <v>1442</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>349</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C125" s="15" t="s">
-        <v>916</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1443</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C127" s="13" t="s">
-        <v>355</v>
+        <v>352</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>917</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>356</v>
+        <v>1115</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
+        <v>353</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
         <v>358</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B129" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="C128" s="13" t="s">
+      <c r="C129" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="D129" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="E128" s="3" t="s">
+      <c r="E129" s="3" t="s">
         <v>1445</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
+    <row r="130" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
         <v>363</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B130" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C129" s="15" t="s">
+      <c r="C130" s="15" t="s">
         <v>876</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="D130" s="3" t="s">
         <v>1079</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E130" s="3" t="s">
         <v>978</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>365</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C130" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>1254</v>
+        <v>172</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>182</v>
+        <v>1254</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="15" t="s">
-        <v>918</v>
+        <v>186</v>
+      </c>
+      <c r="C134" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>1593</v>
+        <v>188</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>1024</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>751</v>
+        <v>371</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C136" s="13" t="s">
-        <v>172</v>
+        <v>372</v>
+      </c>
+      <c r="C136" s="15" t="s">
+        <v>919</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>173</v>
+        <v>1594</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>1446</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="C137" s="15" t="s">
-        <v>1255</v>
+        <v>171</v>
+      </c>
+      <c r="C137" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>1595</v>
+        <v>173</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C138" s="13" t="s">
-        <v>1254</v>
+        <v>753</v>
+      </c>
+      <c r="C138" s="15" t="s">
+        <v>1255</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>178</v>
+        <v>1595</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="C139" s="15" t="s">
-        <v>1256</v>
+        <v>176</v>
+      </c>
+      <c r="C139" s="13" t="s">
+        <v>1254</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>1596</v>
+        <v>178</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>1169</v>
+        <v>1259</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>1260</v>
+        <v>1169</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>373</v>
+        <v>765</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="C145" s="13" t="s">
-        <v>375</v>
+        <v>766</v>
+      </c>
+      <c r="C145" s="15" t="s">
+        <v>1260</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>376</v>
+        <v>1601</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>767</v>
+        <v>373</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="C146" s="15" t="s">
-        <v>1261</v>
+        <v>374</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>375</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>1602</v>
+        <v>376</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C147" s="13" t="s">
-        <v>304</v>
+        <v>768</v>
+      </c>
+      <c r="C147" s="15" t="s">
+        <v>1261</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>305</v>
+        <v>1602</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>1376</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="C148" s="15" t="s">
-        <v>1262</v>
+        <v>303</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>304</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>1603</v>
+        <v>305</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>1459</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>773</v>
+        <v>1603</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>1604</v>
+        <v>773</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>392</v>
+        <v>777</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>926</v>
+        <v>1265</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>1122</v>
+        <v>1605</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>1032</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>780</v>
+        <v>392</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>1266</v>
+        <v>926</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>1606</v>
+        <v>1122</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>1463</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
+        <v>781</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="C155" s="15" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
         <v>783</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B156" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="C155" s="15" t="s">
+      <c r="C156" s="15" t="s">
         <v>1268</v>
       </c>
-      <c r="D155" s="3" t="s">
+      <c r="D156" s="3" t="s">
         <v>1608</v>
       </c>
-      <c r="E155" s="3" t="s">
+      <c r="E156" s="3" t="s">
         <v>1465</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
+    <row r="157" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
         <v>378</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B157" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="C156" s="15" t="s">
+      <c r="C157" s="15" t="s">
         <v>920</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="D157" s="3" t="s">
         <v>1116</v>
       </c>
-      <c r="E156" s="3" t="s">
+      <c r="E157" s="3" t="s">
         <v>1026</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>380</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="C157" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>1457</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>785</v>
+        <v>380</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>374</v>
@@ -14857,686 +14918,737 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>787</v>
-      </c>
-      <c r="C159" s="15" t="s">
-        <v>1269</v>
+        <v>374</v>
+      </c>
+      <c r="C159" s="13" t="s">
+        <v>375</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>1609</v>
+        <v>376</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>1466</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>381</v>
+        <v>788</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>384</v>
+        <v>790</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>922</v>
+        <v>1271</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>1118</v>
+        <v>1611</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>1028</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
+        <v>383</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C163" s="15" t="s">
+        <v>922</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
         <v>385</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B164" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="C163" s="15" t="s">
+      <c r="C164" s="15" t="s">
         <v>923</v>
       </c>
-      <c r="D163" s="3" t="s">
+      <c r="D164" s="3" t="s">
         <v>1119</v>
       </c>
-      <c r="E163" s="3" t="s">
+      <c r="E164" s="3" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
+    <row r="165" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
         <v>387</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B165" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="15" t="s">
+      <c r="C165" s="15" t="s">
         <v>924</v>
       </c>
-      <c r="D164" s="3" t="s">
+      <c r="D165" s="3" t="s">
         <v>1120</v>
       </c>
-      <c r="E164" s="3" t="s">
+      <c r="E165" s="3" t="s">
         <v>1030</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>389</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="C165" s="15" t="s">
-        <v>925</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
+        <v>395</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C169" s="15" t="s">
+        <v>928</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
         <v>397</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B170" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="C169" s="15" t="s">
+      <c r="C170" s="15" t="s">
         <v>929</v>
       </c>
-      <c r="D169" s="3" t="s">
+      <c r="D170" s="3" t="s">
         <v>1125</v>
       </c>
-      <c r="E169" s="3" t="s">
+      <c r="E170" s="3" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
+    <row r="171" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
         <v>791</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B171" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="C170" s="15" t="s">
+      <c r="C171" s="15" t="s">
         <v>1272</v>
       </c>
-      <c r="D170" s="3" t="s">
+      <c r="D171" s="3" t="s">
         <v>1612</v>
       </c>
-      <c r="E170" s="3" t="s">
+      <c r="E171" s="3" t="s">
         <v>1469</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
+    <row r="172" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
         <v>793</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B172" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="C171" s="15" t="s">
+      <c r="C172" s="15" t="s">
         <v>1273</v>
       </c>
-      <c r="D171" s="3" t="s">
+      <c r="D172" s="3" t="s">
         <v>1613</v>
       </c>
-      <c r="E171" s="3" t="s">
+      <c r="E172" s="3" t="s">
         <v>1470</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
+    <row r="173" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
         <v>795</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B173" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="C172" s="15" t="s">
+      <c r="C173" s="15" t="s">
         <v>1274</v>
       </c>
-      <c r="D172" s="3" t="s">
+      <c r="D173" s="3" t="s">
         <v>1614</v>
       </c>
-      <c r="E172" s="3" t="s">
+      <c r="E173" s="3" t="s">
         <v>1471</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
         <v>797</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B174" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="15" t="s">
+      <c r="C174" s="15" t="s">
         <v>925</v>
       </c>
-      <c r="D173" s="3" t="s">
+      <c r="D174" s="3" t="s">
         <v>1121</v>
       </c>
-      <c r="E173" s="3" t="s">
+      <c r="E174" s="3" t="s">
         <v>1472</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
+    <row r="175" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
         <v>798</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B175" s="4" t="s">
         <v>799</v>
       </c>
-      <c r="C174" s="15" t="s">
+      <c r="C175" s="15" t="s">
         <v>1275</v>
       </c>
-      <c r="D174" s="3" t="s">
+      <c r="D175" s="3" t="s">
         <v>1615</v>
       </c>
-      <c r="E174" s="3" t="s">
+      <c r="E175" s="3" t="s">
         <v>1473</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
         <v>800</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B176" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="C175" s="15" t="s">
+      <c r="C176" s="15" t="s">
         <v>927</v>
       </c>
-      <c r="D175" s="3" t="s">
+      <c r="D176" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="E175" s="3" t="s">
+      <c r="E176" s="3" t="s">
         <v>1033</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
-        <v>801</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>802</v>
-      </c>
-      <c r="C176" s="15" t="s">
-        <v>1276</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>1616</v>
-      </c>
-      <c r="E176" s="3" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
+        <v>801</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="C177" s="15" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
         <v>803</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B178" s="4" t="s">
         <v>804</v>
       </c>
-      <c r="C177" s="15" t="s">
+      <c r="C178" s="15" t="s">
         <v>1277</v>
       </c>
-      <c r="D177" s="3" t="s">
+      <c r="D178" s="3" t="s">
         <v>1617</v>
       </c>
-      <c r="E177" s="3" t="s">
+      <c r="E178" s="3" t="s">
         <v>1475</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>399</v>
-      </c>
-      <c r="B178" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="C178" s="15" t="s">
-        <v>930</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>1126</v>
+        <v>400</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="C180" s="13" t="s">
-        <v>405</v>
+        <v>402</v>
+      </c>
+      <c r="C180" s="15" t="s">
+        <v>931</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>406</v>
+        <v>1126</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>1476</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C181" s="13" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="C182" s="15" t="s">
-        <v>932</v>
+        <v>409</v>
+      </c>
+      <c r="C182" s="13" t="s">
+        <v>409</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>1127</v>
+        <v>410</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>1038</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="C183" s="13" t="s">
-        <v>1172</v>
+        <v>413</v>
+      </c>
+      <c r="C183" s="15" t="s">
+        <v>932</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>417</v>
+        <v>1127</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>1478</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C184" s="15" t="s">
-        <v>933</v>
+        <v>415</v>
+      </c>
+      <c r="C184" s="13" t="s">
+        <v>1172</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>1128</v>
+        <v>417</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>1039</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
+        <v>419</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C185" s="15" t="s">
+        <v>933</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
         <v>421</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B186" s="4" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C186" s="15" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D186" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E186" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="16" x14ac:dyDescent="0.4">
+      <c r="A187" t="s">
+        <v>805</v>
+      </c>
+      <c r="B187" s="20" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D187" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E187" t="s">
         <v>1643</v>
-      </c>
-      <c r="C185" s="15" t="s">
-        <v>1654</v>
-      </c>
-      <c r="D185" t="s">
-        <v>1657</v>
-      </c>
-      <c r="E185" t="s">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" ht="16" x14ac:dyDescent="0.4">
-      <c r="A186" t="s">
-        <v>805</v>
-      </c>
-      <c r="B186" s="20" t="s">
-        <v>1644</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1655</v>
-      </c>
-      <c r="D186" t="s">
-        <v>1658</v>
-      </c>
-      <c r="E186" t="s">
-        <v>1661</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
-        <v>422</v>
-      </c>
-      <c r="B187" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="C187" s="15" t="s">
-        <v>934</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>1129</v>
-      </c>
-      <c r="E187" s="3" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C188" s="15" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>1643</v>
+        <v>420</v>
       </c>
       <c r="C189" s="15" t="s">
-        <v>1654</v>
-      </c>
-      <c r="D189" t="s">
-        <v>1657</v>
-      </c>
-      <c r="E189" t="s">
-        <v>1660</v>
+        <v>933</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>1039</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>400</v>
+        <v>1633</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>930</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E190" s="3" t="s">
-        <v>1036</v>
+        <v>1636</v>
+      </c>
+      <c r="D190" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E190" t="s">
+        <v>1642</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>1126</v>
+        <v>400</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>806</v>
+        <v>427</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="C192" s="15" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>808</v>
+        <v>420</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>1278</v>
+        <v>933</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>1618</v>
+        <v>1128</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>1479</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
+        <v>807</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="C194" s="15" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
         <v>809</v>
       </c>
-      <c r="B194" s="4" t="s">
-        <v>1643</v>
-      </c>
-      <c r="C194" s="15" t="s">
+      <c r="B195" s="4" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C195" s="15" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D195" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E195" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>810</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C196" s="15" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A197" s="7" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A198" s="7" t="s">
         <v>1654</v>
       </c>
-      <c r="D194" t="s">
+      <c r="B198" s="9" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C198" s="9" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D198" s="9" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E198" s="9" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A199" s="7" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B199" s="9" t="s">
         <v>1657</v>
       </c>
-      <c r="E194" t="s">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
-        <v>810</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C195" s="15" t="s">
+      <c r="C199" s="9" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A200" s="7" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B200" s="9" t="s">
         <v>1656</v>
       </c>
-      <c r="D195" t="s">
+      <c r="C200" s="9" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D200" s="9" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E200" s="9" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A201" s="7" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B201" s="9" t="s">
         <v>1659</v>
       </c>
-      <c r="E195" t="s">
-        <v>1662</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A196" s="7" t="s">
-        <v>1630</v>
-      </c>
-      <c r="B196" s="9" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C196" s="8" t="s">
-        <v>1648</v>
-      </c>
-      <c r="D196" s="7" t="s">
-        <v>1650</v>
-      </c>
-      <c r="E196" s="7" t="s">
-        <v>1652</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A197" s="7" t="s">
-        <v>1635</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>1636</v>
-      </c>
-      <c r="C197" s="8" t="s">
-        <v>1642</v>
-      </c>
-      <c r="D197" s="7" t="s">
-        <v>1641</v>
-      </c>
-      <c r="E197" s="7" t="s">
-        <v>1637</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A198" s="7" t="s">
-        <v>1638</v>
-      </c>
-      <c r="B198" s="9" t="s">
-        <v>1646</v>
-      </c>
-      <c r="C198" s="7" t="s">
-        <v>1649</v>
-      </c>
-      <c r="D198" s="7" t="s">
-        <v>1651</v>
-      </c>
-      <c r="E198" s="7" t="s">
-        <v>1653</v>
+      <c r="C201" s="9" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>1659</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E195" xr:uid="{B01EA010-864B-8746-BF5D-2E469295667F}"/>
+  <autoFilter ref="A1:E196" xr:uid="{B01EA010-864B-8746-BF5D-2E469295667F}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/src/R/translations.xlsx
+++ b/src/R/translations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5aee5c5b004427f/Documents/mr-risk-assessment/src/R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{132F1232-AAEB-42DF-9114-B0462C5F7248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{278938BD-8EEF-4A72-B5CF-EA4A40E5C537}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{132F1232-AAEB-42DF-9114-B0462C5F7248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BECB1E7C-0063-4013-8909-EA7982EEF09C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{41A3C097-9B5C-484B-88DA-6A6C7D19F152}"/>
+    <workbookView xWindow="110" yWindow="110" windowWidth="19180" windowHeight="10060" xr2:uid="{41A3C097-9B5C-484B-88DA-6A6C7D19F152}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2310" uniqueCount="1681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2310" uniqueCount="1674">
   <si>
     <t>LABEL</t>
   </si>
@@ -673,9 +673,6 @@
     <t>title_figure_5c</t>
   </si>
   <si>
-    <t>Presencia de población vulnerable</t>
-  </si>
-  <si>
     <t>title_section_6</t>
   </si>
   <si>
@@ -1213,9 +1210,6 @@
     <t>vul_title_map_total_pr</t>
   </si>
   <si>
-    <t>Evaluación de riesgo para grupos vulnerables</t>
-  </si>
-  <si>
     <t>vul_title_map_inter_pob</t>
   </si>
   <si>
@@ -2059,9 +2053,6 @@
     <t>general_other_ind</t>
   </si>
   <si>
-    <t>Otros indicadores</t>
-  </si>
-  <si>
     <t>table_admin1_name</t>
   </si>
   <si>
@@ -2230,15 +2221,6 @@
     <t>Distribución</t>
   </si>
   <si>
-    <t>Tasa anual de casos sospechosos de sarampión y rubéola por 100 000 habitantes</t>
-  </si>
-  <si>
-    <t>Annual rate of suspected measles and rubella cases per 100,000 population</t>
-  </si>
-  <si>
-    <t>Casos suspeitos de sarampo e rubéola por 100.000 habitantes</t>
-  </si>
-  <si>
     <t>Cases with adequate investigation</t>
   </si>
   <si>
@@ -2437,9 +2419,6 @@
     <t>Población vulnerable (Puntaje)</t>
   </si>
   <si>
-    <t>Evaluación de riesgo por grupos vulnerables</t>
-  </si>
-  <si>
     <t>vul_subtitle_inter_pob</t>
   </si>
   <si>
@@ -2739,9 +2718,6 @@
     <t>Population density (per</t>
   </si>
   <si>
-    <t>Presence of vulnerable population</t>
-  </si>
-  <si>
     <t>Rapid response to imported cases</t>
   </si>
   <si>
@@ -2862,9 +2838,6 @@
     <t>Risk assessment for threat assessment</t>
   </si>
   <si>
-    <t>Risk assessment for vulnerable groups</t>
-  </si>
-  <si>
     <t>Presence of migrant population</t>
   </si>
   <si>
@@ -3539,18 +3512,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Présence de populations vulnérables</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Réponse rapide pour les cas importés</t>
     </r>
   </si>
@@ -4131,18 +4092,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Évaluation de la menace pour les groupes vulnérables</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Présence de populations migrantes</t>
     </r>
   </si>
@@ -4434,9 +4383,6 @@
     <t>Densidade populacional (por</t>
   </si>
   <si>
-    <t>Presença de população vulnerável</t>
-  </si>
-  <si>
     <t>Resposta rápida a casos importados</t>
   </si>
   <si>
@@ -4536,9 +4482,6 @@
     <t>Avaliação de risco para avaliação da ameaça</t>
   </si>
   <si>
-    <t>Avaliação de risco para grupos vulneráveis</t>
-  </si>
-  <si>
     <t>Presença de população migrante</t>
   </si>
   <si>
@@ -4848,9 +4791,6 @@
     <t>Risk points (general scale)</t>
   </si>
   <si>
-    <t>Additional indicators</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
@@ -4998,9 +4938,6 @@
     <t>Vulnerable population (Score)</t>
   </si>
   <si>
-    <t>Risk assessment by vulnerable groups</t>
-  </si>
-  <si>
     <t>Presence of migrant population, internally displaced population, slums, or Indigenous communities;</t>
   </si>
   <si>
@@ -5870,18 +5807,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Autres indicateurs</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Municipalité</t>
     </r>
   </si>
@@ -6194,18 +6119,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Taux annuel de cas suspects de rougeole et de rubéole pour 100 000 habitants</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Cas avec prélèvement adéquat d'échantillons</t>
     </r>
   </si>
@@ -6650,18 +6563,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Évaluation du risque par groupes vulnérables</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Présence de population migrante, de personnes déplacées à l’intérieure du pays, de quartiers défavorisés ou de communautés autochtones</t>
     </r>
   </si>
@@ -7053,9 +6954,6 @@
     <t>Pontos de risco (escala geral)</t>
   </si>
   <si>
-    <t>Outros indicadores</t>
-  </si>
-  <si>
     <t>Dados</t>
   </si>
   <si>
@@ -7179,9 +7077,6 @@
     <t>População vulnerável (Pontuação)</t>
   </si>
   <si>
-    <t>Avaliação de risco por grupos vulneráveis</t>
-  </si>
-  <si>
     <t>Presença de população migrante, população deslocada internamente, favelas ou comunidades indígenas</t>
   </si>
   <si>
@@ -7290,30 +7185,12 @@
     <t>Présence d'une équipe formée au cours des 2 dernières années (Score)</t>
   </si>
   <si>
-    <t>Presencia de un equipo capacitado en los últimos 2 años</t>
-  </si>
-  <si>
-    <t>Presence of a trained team in the last 2 years</t>
-  </si>
-  <si>
-    <t>Presença de uma equipe treinada nos últimos 2 anos</t>
-  </si>
-  <si>
-    <t>Présence d'une équipe formée au cours des 2 dernières années</t>
-  </si>
-  <si>
-    <t>Áreas subnacionais (estadual) com uma equipe que foi treinada para resposta a surtos nos últimos 2 anos</t>
-  </si>
-  <si>
     <t>case_class_lab</t>
   </si>
   <si>
     <t>Distribución espacial de municipios notificando casos de sarampión y rubeola</t>
   </si>
   <si>
-    <t>Número de municipios que reportan casos</t>
-  </si>
-  <si>
     <t>case_class_infobox_text</t>
   </si>
   <si>
@@ -7332,9 +7209,6 @@
     <t>case_class_lab_short</t>
   </si>
   <si>
-    <t>Casos reportados</t>
-  </si>
-  <si>
     <t>Spatial distribution of municipalities reporting measles and rubella cases</t>
   </si>
   <si>
@@ -7365,12 +7239,6 @@
     <t>Signale des cas confirmés</t>
   </si>
   <si>
-    <t>Reported cases</t>
-  </si>
-  <si>
-    <t>Cas signalés</t>
-  </si>
-  <si>
     <t>case_class_infobox_pct</t>
   </si>
   <si>
@@ -7396,6 +7264,72 @@
   </si>
   <si>
     <t>Cas confirmés</t>
+  </si>
+  <si>
+    <t>Puntos de otros indicadores</t>
+  </si>
+  <si>
+    <t>Points from other indicators</t>
+  </si>
+  <si>
+    <t>Pontos de outros indicadores</t>
+  </si>
+  <si>
+    <t>Points de autres indicateurs</t>
+  </si>
+  <si>
+    <t>Minicipalidades notificando casos</t>
+  </si>
+  <si>
+    <t>Municípios notificando casos</t>
+  </si>
+  <si>
+    <t>Municipalités signalant des cas confirmés</t>
+  </si>
+  <si>
+    <t>Tasa anual de casos sospechosos de SR por 100 000 habitantes</t>
+  </si>
+  <si>
+    <t>Annual rate of suspected MR cases per 100,000 population</t>
+  </si>
+  <si>
+    <t>Casos suspeitos de SR por 100.000 habitantes</t>
+  </si>
+  <si>
+    <t>Taux annuel de cas suspects de SR pour 100 000 habitants</t>
+  </si>
+  <si>
+    <t>Municipalities reporting cases</t>
+  </si>
+  <si>
+    <t>Vulnerability by vulnerable groups</t>
+  </si>
+  <si>
+    <t>Vulnerabilidad por grupos vulnerables</t>
+  </si>
+  <si>
+    <t>Vulnerabilidade por grupos vulneráveis</t>
+  </si>
+  <si>
+    <t>Vulnérabilité par groupes vulnérables</t>
+  </si>
+  <si>
+    <t>Teams trained in the last 2 years</t>
+  </si>
+  <si>
+    <t>Equipos capacitados en los últimos 2 años</t>
+  </si>
+  <si>
+    <t>Vulnerabilidad para grupos vulnerables</t>
+  </si>
+  <si>
+    <t>Vulnerability for vulnerable groups</t>
+  </si>
+  <si>
+    <t>Vulnerabilidade para grupos vulneráveis</t>
+  </si>
+  <si>
+    <t>Vulnerabilité pour les groupes vulnérables</t>
   </si>
 </sst>
 </file>
@@ -7405,6 +7339,13 @@
   <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -7500,12 +7441,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -7535,60 +7470,62 @@
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8055,13 +7992,13 @@
         <v>26</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -8072,13 +8009,13 @@
         <v>28</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -8089,13 +8026,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -8106,13 +8043,13 @@
         <v>32</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -8123,13 +8060,13 @@
         <v>34</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -8140,13 +8077,13 @@
         <v>36</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="108.5" x14ac:dyDescent="0.35">
@@ -8157,13 +8094,13 @@
         <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="139.5" x14ac:dyDescent="0.35">
@@ -8171,16 +8108,16 @@
         <v>39</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>1130</v>
+        <v>1117</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -8262,10 +8199,10 @@
         <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -8276,13 +8213,13 @@
         <v>63</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -8293,13 +8230,13 @@
         <v>65</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -8310,13 +8247,13 @@
         <v>67</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1047</v>
+        <v>1036</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -8327,13 +8264,13 @@
         <v>69</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1048</v>
+        <v>1037</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -8344,13 +8281,13 @@
         <v>71</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1049</v>
+        <v>1038</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -8378,13 +8315,13 @@
         <v>78</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1050</v>
+        <v>1039</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -8395,13 +8332,13 @@
         <v>80</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="108.5" x14ac:dyDescent="0.35">
@@ -8412,13 +8349,13 @@
         <v>82</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1052</v>
+        <v>1041</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="139.5" x14ac:dyDescent="0.35">
@@ -8429,13 +8366,13 @@
         <v>84</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1053</v>
+        <v>1042</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="93" x14ac:dyDescent="0.35">
@@ -8443,16 +8380,16 @@
         <v>85</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1054</v>
+        <v>1043</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1055</v>
+        <v>1044</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="62" x14ac:dyDescent="0.35">
@@ -8463,13 +8400,13 @@
         <v>87</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1056</v>
+        <v>1045</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="93" x14ac:dyDescent="0.35">
@@ -8480,13 +8417,13 @@
         <v>89</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1057</v>
+        <v>1046</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="220" customHeight="1" x14ac:dyDescent="0.35">
@@ -8497,13 +8434,13 @@
         <v>91</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1058</v>
+        <v>1047</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -8514,13 +8451,13 @@
         <v>93</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1059</v>
+        <v>1048</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -8531,7 +8468,7 @@
         <v>95</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>95</v>
@@ -8551,10 +8488,10 @@
         <v>96</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -8565,13 +8502,13 @@
         <v>99</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>99</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -8582,7 +8519,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>101</v>
@@ -8599,13 +8536,13 @@
         <v>103</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1061</v>
+        <v>1050</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -8616,13 +8553,13 @@
         <v>105</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1062</v>
+        <v>1051</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -8633,13 +8570,13 @@
         <v>107</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1063</v>
+        <v>1052</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -8650,13 +8587,13 @@
         <v>109</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1064</v>
+        <v>1053</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -8667,13 +8604,13 @@
         <v>111</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1065</v>
+        <v>1054</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -8684,13 +8621,13 @@
         <v>113</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -8701,13 +8638,13 @@
         <v>115</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1067</v>
+        <v>1056</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -8718,13 +8655,13 @@
         <v>117</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1068</v>
+        <v>1057</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -8752,13 +8689,13 @@
         <v>124</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1069</v>
+        <v>1058</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8769,13 +8706,13 @@
         <v>126</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1070</v>
+        <v>1059</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -8854,13 +8791,13 @@
         <v>148</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1071</v>
+        <v>1060</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -8871,13 +8808,13 @@
         <v>150</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>1072</v>
+        <v>1061</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -8888,13 +8825,13 @@
         <v>152</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>1073</v>
+        <v>1062</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="77.5" x14ac:dyDescent="0.35">
@@ -8905,13 +8842,13 @@
         <v>154</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>1074</v>
+        <v>1063</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -8922,13 +8859,13 @@
         <v>156</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>1075</v>
+        <v>1064</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
@@ -8939,13 +8876,13 @@
         <v>158</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>1076</v>
+        <v>1065</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -8956,30 +8893,30 @@
         <v>160</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1077</v>
+        <v>1066</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>976</v>
+        <v>967</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1632</v>
+        <v>1612</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>1651</v>
+        <v>1626</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>1660</v>
+        <v>1633</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1661</v>
+        <v>1634</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>1662</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
@@ -9007,13 +8944,13 @@
         <v>167</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1078</v>
+        <v>1067</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>977</v>
+        <v>968</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.35">
@@ -9024,13 +8961,13 @@
         <v>169</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>1079</v>
+        <v>1068</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -9126,13 +9063,13 @@
         <v>196</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1080</v>
+        <v>1069</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -9143,13 +9080,13 @@
         <v>198</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1081</v>
+        <v>1070</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -9160,13 +9097,13 @@
         <v>200</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1082</v>
+        <v>1071</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -9174,633 +9111,633 @@
         <v>201</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>202</v>
+        <v>1665</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>880</v>
+        <v>1664</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1083</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>982</v>
+        <v>1666</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>1667</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>202</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B73" s="4" t="s">
-        <v>204</v>
-      </c>
       <c r="C73" s="15" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1084</v>
+        <v>1072</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>983</v>
+        <v>973</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>204</v>
+      </c>
+      <c r="B74" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="B74" s="17" t="s">
-        <v>206</v>
-      </c>
       <c r="C74" s="15" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>984</v>
+        <v>974</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
+        <v>206</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>208</v>
-      </c>
       <c r="C75" s="15" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>985</v>
+        <v>975</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
+        <v>208</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>210</v>
-      </c>
       <c r="C76" s="15" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>986</v>
+        <v>976</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>211</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1634</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1637</v>
+        <v>210</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>1668</v>
       </c>
       <c r="D77" t="s">
-        <v>1649</v>
+        <v>1619</v>
       </c>
       <c r="E77" t="s">
-        <v>1643</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
+        <v>211</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>213</v>
-      </c>
       <c r="C78" s="15" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
+        <v>213</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="B79" s="4" t="s">
-        <v>215</v>
-      </c>
       <c r="C79" s="15" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>988</v>
+        <v>978</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>215</v>
+      </c>
+      <c r="B80" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B80" s="4" t="s">
-        <v>217</v>
-      </c>
       <c r="C80" s="15" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>989</v>
+        <v>979</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
+        <v>217</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B81" s="4" t="s">
-        <v>219</v>
-      </c>
       <c r="C81" s="15" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>990</v>
+        <v>980</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>219</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="C82" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
+        <v>224</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="C83" s="15" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
+        <v>226</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>228</v>
-      </c>
       <c r="C84" s="15" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>228</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="C85" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
+        <v>233</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="C86" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="D86" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
+        <v>238</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B87" s="4" t="s">
-        <v>240</v>
-      </c>
       <c r="C87" s="3" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>993</v>
+        <v>983</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
+        <v>240</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="C88" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>244</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B89" s="4" t="s">
-        <v>246</v>
-      </c>
       <c r="C89" s="15" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>994</v>
+        <v>984</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
+        <v>246</v>
+      </c>
+      <c r="B90" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>248</v>
-      </c>
       <c r="C90" s="15" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>995</v>
+        <v>985</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
+        <v>248</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>250</v>
-      </c>
       <c r="C91" s="15" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>996</v>
+        <v>986</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
+        <v>250</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B92" s="4" t="s">
-        <v>252</v>
-      </c>
       <c r="C92" s="15" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>997</v>
+        <v>987</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>994</v>
+        <v>984</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>989</v>
+        <v>979</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
+        <v>254</v>
+      </c>
+      <c r="B95" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>256</v>
-      </c>
       <c r="C95" s="15" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>998</v>
+        <v>988</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
+        <v>256</v>
+      </c>
+      <c r="B96" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B96" s="4" t="s">
-        <v>258</v>
-      </c>
       <c r="C96" s="15" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>999</v>
+        <v>989</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
+        <v>258</v>
+      </c>
+      <c r="B97" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B97" s="4" t="s">
-        <v>260</v>
-      </c>
       <c r="C97" s="15" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
+        <v>260</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B98" s="4" t="s">
-        <v>262</v>
-      </c>
       <c r="C98" s="15" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>1001</v>
+        <v>991</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
+        <v>262</v>
+      </c>
+      <c r="B99" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B99" s="4" t="s">
-        <v>264</v>
-      </c>
       <c r="C99" s="15" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>1002</v>
+        <v>992</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
+        <v>264</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B100" s="4" t="s">
-        <v>266</v>
-      </c>
       <c r="C100" s="15" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1101</v>
+        <v>1089</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>1003</v>
+        <v>993</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>998</v>
+        <v>988</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>989</v>
+        <v>979</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
+        <v>268</v>
+      </c>
+      <c r="B103" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="C103" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="E103" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
+        <v>273</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="C104" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="D104" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="E104" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
+        <v>278</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="C105" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="D105" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="E105" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
+        <v>283</v>
+      </c>
+      <c r="B106" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="C106" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="D106" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="E106" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
+        <v>288</v>
+      </c>
+      <c r="B107" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="C107" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="D107" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E107" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
+        <v>292</v>
+      </c>
+      <c r="B108" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="C108" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="D108" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="E108" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>41</v>
@@ -9817,7 +9754,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>46</v>
@@ -9834,7 +9771,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>51</v>
@@ -9851,7 +9788,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>56</v>
@@ -9868,75 +9805,75 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
+        <v>301</v>
+      </c>
+      <c r="B113" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="C113" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="D113" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="E113" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B114" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="D114" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="E114" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
+        <v>307</v>
+      </c>
+      <c r="B115" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="C115" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="D115" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="E115" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
+        <v>312</v>
+      </c>
+      <c r="B116" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B116" s="4" t="s">
-        <v>314</v>
-      </c>
       <c r="C116" s="3" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="D116" t="s">
-        <v>1070</v>
+        <v>1059</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>1004</v>
+        <v>994</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>128</v>
@@ -9953,381 +9890,381 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
+        <v>315</v>
+      </c>
+      <c r="B118" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B118" s="4" t="s">
-        <v>317</v>
-      </c>
       <c r="C118" s="15" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1005</v>
+        <v>995</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
+        <v>317</v>
+      </c>
+      <c r="B119" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B119" s="4" t="s">
-        <v>319</v>
-      </c>
       <c r="C119" s="15" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="D119" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
+        <v>319</v>
+      </c>
+      <c r="B120" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B120" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="C120" s="15" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="D120" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
+        <v>321</v>
+      </c>
+      <c r="B121" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B121" s="4" t="s">
-        <v>323</v>
-      </c>
       <c r="C121" s="15" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="D121" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
+        <v>323</v>
+      </c>
+      <c r="B122" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B122" s="4" t="s">
-        <v>325</v>
-      </c>
       <c r="C122" s="15" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="D122" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>1009</v>
+        <v>999</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
+        <v>325</v>
+      </c>
+      <c r="B123" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B123" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="C123" s="15" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="D123" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
+        <v>327</v>
+      </c>
+      <c r="B124" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B124" s="4" t="s">
-        <v>329</v>
-      </c>
       <c r="C124" s="15" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="D124" t="s">
-        <v>1106</v>
+        <v>1094</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1011</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
+        <v>329</v>
+      </c>
+      <c r="B125" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="B125" s="4" t="s">
-        <v>331</v>
-      </c>
       <c r="C125" s="15" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1012</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
+        <v>331</v>
+      </c>
+      <c r="B126" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B126" s="4" t="s">
-        <v>333</v>
-      </c>
       <c r="C126" s="15" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="D126" t="s">
-        <v>1072</v>
+        <v>1061</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
+        <v>333</v>
+      </c>
+      <c r="B127" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B127" s="4" t="s">
-        <v>335</v>
-      </c>
       <c r="C127" s="15" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="D127" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1014</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="D128" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
+        <v>336</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="B129" s="4" t="s">
-        <v>338</v>
-      </c>
       <c r="C129" s="15" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="D129" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>1015</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
+        <v>338</v>
+      </c>
+      <c r="B130" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="B130" s="4" t="s">
-        <v>340</v>
-      </c>
       <c r="C130" s="15" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D130" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>1016</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
+        <v>340</v>
+      </c>
+      <c r="B131" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B131" s="4" t="s">
-        <v>342</v>
-      </c>
       <c r="C131" s="15" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="D131" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>1017</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
+        <v>342</v>
+      </c>
+      <c r="B132" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="B132" s="4" t="s">
-        <v>344</v>
-      </c>
       <c r="C132" s="15" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>1018</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
+        <v>344</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="B133" s="4" t="s">
-        <v>346</v>
-      </c>
       <c r="C133" s="15" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="D133" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>1019</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
+        <v>346</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="B134" s="4" t="s">
-        <v>348</v>
-      </c>
       <c r="C134" s="15" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="D134" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>1020</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
+        <v>348</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="B135" s="4" t="s">
-        <v>350</v>
-      </c>
       <c r="C135" s="15" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="D135" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>1021</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
+        <v>350</v>
+      </c>
+      <c r="B136" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="B136" s="4" t="s">
-        <v>352</v>
-      </c>
       <c r="C136" s="15" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="D136" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>1022</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
+        <v>352</v>
+      </c>
+      <c r="B137" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="C137" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="D137" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="E137" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
+        <v>357</v>
+      </c>
+      <c r="B138" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="C138" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="D138" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="E138" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
+        <v>362</v>
+      </c>
+      <c r="B139" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B139" s="4" t="s">
-        <v>364</v>
-      </c>
       <c r="C139" s="3" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>1079</v>
+        <v>1068</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>171</v>
@@ -10344,7 +10281,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>176</v>
@@ -10361,7 +10298,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>181</v>
@@ -10378,7 +10315,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>186</v>
@@ -10395,568 +10332,568 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
+        <v>368</v>
+      </c>
+      <c r="B144" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="B144" s="4" t="s">
-        <v>370</v>
-      </c>
       <c r="C144" s="15" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>173</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
+        <v>370</v>
+      </c>
+      <c r="B145" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="B145" s="4" t="s">
-        <v>372</v>
-      </c>
       <c r="C145" s="15" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>1025</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
+        <v>372</v>
+      </c>
+      <c r="B146" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="C146" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="D146" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D146" s="3" t="s">
+      <c r="E146" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
+        <v>377</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="B147" s="4" t="s">
-        <v>379</v>
-      </c>
       <c r="C147" s="15" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="D147" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>1026</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B148" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C148" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="D148" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="E148" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>382</v>
+        <v>1670</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>921</v>
+        <v>1671</v>
       </c>
       <c r="D149" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>1027</v>
+        <v>1672</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>1673</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="D150" t="s">
-        <v>1118</v>
+        <v>1105</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="D151" t="s">
-        <v>1119</v>
+        <v>1106</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>1120</v>
+        <v>1107</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="D153" t="s">
-        <v>1121</v>
+        <v>1108</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="D154" t="s">
-        <v>1122</v>
+        <v>1109</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="D155" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="D156" t="s">
-        <v>1124</v>
+        <v>1111</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="D157" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="D158" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="D159" t="s">
-        <v>1126</v>
+        <v>1113</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
+        <v>401</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="D160" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="E160" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
+        <v>406</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D161" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="E161" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="D162" t="s">
-        <v>1127</v>
+        <v>1114</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
+        <v>412</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C163" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="D163" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="E163" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="D164" t="s">
-        <v>1128</v>
+        <v>1115</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>421</v>
-      </c>
-      <c r="B165" t="s">
-        <v>1634</v>
-      </c>
-      <c r="C165" t="s">
-        <v>1637</v>
+        <v>419</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C165" s="15" t="s">
+        <v>1668</v>
       </c>
       <c r="D165" t="s">
-        <v>1640</v>
+        <v>1619</v>
       </c>
       <c r="E165" t="s">
-        <v>1643</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="D166" t="s">
-        <v>1129</v>
+        <v>1116</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="D167" t="s">
-        <v>1128</v>
+        <v>1115</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>425</v>
-      </c>
-      <c r="B168" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1646</v>
+        <v>423</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C168" s="15" t="s">
+        <v>1668</v>
       </c>
       <c r="D168" t="s">
-        <v>1647</v>
+        <v>1619</v>
       </c>
       <c r="E168" t="s">
-        <v>1648</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>930</v>
+        <v>403</v>
       </c>
       <c r="D169" t="s">
-        <v>400</v>
-      </c>
-      <c r="E169" s="3" t="s">
-        <v>1036</v>
+        <v>404</v>
+      </c>
+      <c r="E169" s="4" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>931</v>
+        <v>407</v>
       </c>
       <c r="D170" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E170" s="3" t="s">
-        <v>1037</v>
+        <v>408</v>
+      </c>
+      <c r="E170" s="4" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>1651</v>
+        <v>1626</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>1660</v>
+        <v>1633</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>1661</v>
+        <v>1634</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>1662</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
-        <v>1654</v>
+        <v>1628</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>1630</v>
+        <v>1610</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>1663</v>
+        <v>1636</v>
       </c>
       <c r="D172" s="9" t="s">
-        <v>1664</v>
+        <v>1637</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>1631</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
-        <v>1653</v>
+        <v>1627</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>1657</v>
+        <v>1631</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>1665</v>
+        <v>1638</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>1666</v>
+        <v>1639</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>1667</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
-        <v>1655</v>
+        <v>1629</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>1656</v>
+        <v>1630</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>1668</v>
+        <v>1641</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>1656</v>
+        <v>1630</v>
       </c>
       <c r="E174" s="9" t="s">
-        <v>1669</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E175" s="9" t="s">
         <v>1658</v>
-      </c>
-      <c r="B175" s="9" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C175" s="9" t="s">
-        <v>1670</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>1659</v>
-      </c>
-      <c r="E175" s="9" t="s">
-        <v>1671</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
-        <v>1672</v>
+        <v>1643</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>1673</v>
+        <v>1644</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>1674</v>
+        <v>1645</v>
       </c>
       <c r="D176" s="9" t="s">
-        <v>1675</v>
+        <v>1646</v>
       </c>
       <c r="E176" s="9" t="s">
-        <v>1676</v>
+        <v>1647</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E170" xr:uid="{064C7D9D-C4E2-B94C-B003-B8DCE10597B7}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -10991,659 +10928,659 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1131</v>
+        <v>1118</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1491</v>
+        <v>1473</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1290</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1132</v>
+        <v>1119</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1291</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="E4" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1493</v>
+        <v>1475</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1133</v>
+        <v>1120</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1494</v>
+        <v>1476</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1292</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1134</v>
+        <v>1121</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1495</v>
+        <v>1477</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1293</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1496</v>
+        <v>1478</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1294</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1136</v>
+        <v>1123</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1497</v>
+        <v>1479</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1295</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1137</v>
+        <v>1124</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1498</v>
+        <v>1480</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1296</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>1138</v>
+        <v>1125</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1499</v>
+        <v>1481</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1297</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1139</v>
+        <v>1126</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1500</v>
+        <v>1482</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1298</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>1140</v>
+        <v>1127</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1501</v>
+        <v>1483</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1299</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1141</v>
+        <v>1128</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1502</v>
+        <v>1484</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>1300</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>1142</v>
+        <v>1129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1503</v>
+        <v>1485</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1301</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>1143</v>
+        <v>1130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1504</v>
+        <v>1486</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1302</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>1144</v>
+        <v>1131</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1505</v>
+        <v>1487</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1303</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>1145</v>
+        <v>1132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1506</v>
+        <v>1488</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1304</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1146</v>
+        <v>1133</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1507</v>
+        <v>1489</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1305</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1147</v>
+        <v>1134</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1306</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>1148</v>
+        <v>1135</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1508</v>
+        <v>1490</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1307</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>1149</v>
+        <v>1136</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1509</v>
+        <v>1491</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1308</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>1150</v>
+        <v>1137</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1510</v>
+        <v>1492</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1309</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1151</v>
+        <v>1138</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1511</v>
+        <v>1493</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1310</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>1152</v>
+        <v>1139</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1512</v>
+        <v>1494</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1311</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>1153</v>
+        <v>1140</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1513</v>
+        <v>1495</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1312</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1514</v>
+        <v>1496</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>1313</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>1154</v>
+        <v>1141</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1515</v>
+        <v>1497</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>1314</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>1155</v>
+        <v>1142</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1516</v>
+        <v>1498</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>1315</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>1156</v>
+        <v>1143</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1517</v>
+        <v>1499</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>1316</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>1157</v>
+        <v>1144</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1518</v>
+        <v>1500</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>1317</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>1158</v>
+        <v>1145</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1519</v>
+        <v>1501</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>1318</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>1159</v>
+        <v>1146</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1520</v>
+        <v>1502</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>1319</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1521</v>
+        <v>1503</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>1320</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>1161</v>
+        <v>1148</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1522</v>
+        <v>1504</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>1321</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>1162</v>
+        <v>1149</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1523</v>
+        <v>1505</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>1322</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>1163</v>
+        <v>1150</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1524</v>
+        <v>1506</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>1323</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>1164</v>
+        <v>1151</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>121</v>
@@ -11654,98 +11591,98 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C41" s="13" t="s">
+        <v>593</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>595</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C42" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1525</v>
+        <v>1507</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>1324</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>1166</v>
+        <v>1153</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1526</v>
+        <v>1508</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>1325</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>1167</v>
+        <v>1154</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1527</v>
+        <v>1509</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>1326</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>162</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>1168</v>
+        <v>1155</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>164</v>
@@ -11756,466 +11693,466 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>1169</v>
+        <v>1156</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1528</v>
+        <v>1510</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>1327</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>1170</v>
+        <v>1157</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1529</v>
+        <v>1511</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>1328</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>1171</v>
+        <v>1158</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>1530</v>
+        <v>1512</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>1329</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>1173</v>
+        <v>1160</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>1531</v>
+        <v>1513</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>1330</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>1174</v>
+        <v>1161</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>1532</v>
+        <v>1514</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>1331</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>1175</v>
+        <v>1162</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1533</v>
+        <v>1515</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>1332</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>1493</v>
+        <v>1475</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>1176</v>
+        <v>1163</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>1534</v>
+        <v>1516</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>1333</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>1177</v>
+        <v>1164</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>1535</v>
+        <v>1517</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>1334</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>1178</v>
+        <v>1165</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>1536</v>
+        <v>1518</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>1335</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>1179</v>
+        <v>1166</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>1537</v>
+        <v>1519</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>1336</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>1180</v>
+        <v>1167</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1538</v>
+        <v>1520</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>1337</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>1181</v>
+        <v>1168</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1539</v>
+        <v>1521</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>1338</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>1182</v>
+        <v>1169</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1540</v>
+        <v>1522</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>1339</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>1183</v>
+        <v>1170</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1541</v>
+        <v>1523</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>1340</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>1184</v>
+        <v>1171</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>1542</v>
+        <v>1524</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>1341</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>1185</v>
+        <v>1172</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1543</v>
+        <v>1525</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>1342</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>1186</v>
+        <v>1173</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1544</v>
+        <v>1526</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>1343</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>1187</v>
+        <v>1174</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1545</v>
+        <v>1527</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>1344</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>1188</v>
+        <v>1175</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1546</v>
+        <v>1528</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>1345</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>1189</v>
+        <v>1176</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>1190</v>
+        <v>1177</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1547</v>
+        <v>1529</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>1346</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>1191</v>
+        <v>1178</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1548</v>
+        <v>1530</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>1347</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>1192</v>
+        <v>1179</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1549</v>
+        <v>1531</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>1348</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>1193</v>
+        <v>1180</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1550</v>
+        <v>1532</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>1194</v>
+        <v>1181</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1551</v>
+        <v>1533</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>1350</v>
+        <v>1335</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{94F5FF65-00C6-6F47-9553-2E4604D763C3}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12249,87 +12186,87 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>570</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>1351</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>573</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>574</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>1352</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>1195</v>
+        <v>1182</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1552</v>
+        <v>1534</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1353</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="D5" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>1354</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>576</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>580</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>581</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>1355</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -12346,7 +12283,7 @@
         <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1356</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -12363,619 +12300,619 @@
         <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1357</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1196</v>
+        <v>1183</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1553</v>
+        <v>1535</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1358</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>1197</v>
+        <v>1184</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1554</v>
+        <v>1536</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1359</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1555</v>
+        <v>1537</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1360</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>1199</v>
+        <v>1186</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1556</v>
+        <v>1538</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1361</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1200</v>
+        <v>1187</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1362</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>1201</v>
+        <v>1188</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1557</v>
+        <v>1539</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1363</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>592</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>593</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>595</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>596</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>1364</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>596</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>599</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>600</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>1365</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1202</v>
+        <v>1189</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1558</v>
+        <v>1540</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1366</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1203</v>
+        <v>1190</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1367</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>604</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>608</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>1368</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>119</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>1164</v>
+        <v>1151</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1369</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>143</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1205</v>
+        <v>1192</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1370</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>162</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1168</v>
+        <v>1155</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>164</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1371</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>191</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>1206</v>
+        <v>1193</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>193</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1372</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>1189</v>
+        <v>1176</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1373</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>1204</v>
+        <v>1191</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1368</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>119</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1164</v>
+        <v>1151</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1369</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>143</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>1205</v>
+        <v>1192</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>145</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1370</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>162</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>1168</v>
+        <v>1155</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>164</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1371</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>191</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>1206</v>
+        <v>1193</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>193</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>1372</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>1189</v>
+        <v>1176</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>1373</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>620</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>622</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>624</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>625</v>
-      </c>
       <c r="E31" s="3" t="s">
-        <v>1374</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>580</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>581</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>1355</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>1207</v>
+        <v>1194</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1559</v>
+        <v>1541</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>1375</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>1376</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>1208</v>
+        <v>1195</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1560</v>
+        <v>1542</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>1377</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="D36" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>1376</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="D37" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>311</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>1378</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>1209</v>
+        <v>1196</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1561</v>
+        <v>1543</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>1379</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>1210</v>
+        <v>1197</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>1380</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>1211</v>
+        <v>1198</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>1381</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>1212</v>
+        <v>1199</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1562</v>
+        <v>1544</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>1382</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>1213</v>
+        <v>1200</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1563</v>
+        <v>1545</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>1383</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>1384</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>643</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>645</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>647</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>648</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>1385</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -12986,18 +12923,18 @@
         <v>26</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>41</v>
@@ -13009,12 +12946,12 @@
         <v>43</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>1386</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>46</v>
@@ -13026,12 +12963,12 @@
         <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>1387</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>51</v>
@@ -13043,12 +12980,12 @@
         <v>53</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>1388</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>56</v>
@@ -13060,24 +12997,24 @@
         <v>58</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>1389</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>1214</v>
+        <v>1201</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1564</v>
+        <v>1546</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>1390</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -13091,10 +13028,10 @@
         <v>96</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>1391</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -13108,491 +13045,491 @@
         <v>60</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1049</v>
+        <v>1038</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>268</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="C54" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="D54" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>1392</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>1393</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>278</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="C56" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="D56" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="E56" s="3" t="s">
-        <v>1394</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>283</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="C57" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="D57" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="E57" s="3" t="s">
-        <v>1395</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>288</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="C58" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>291</v>
-      </c>
       <c r="D58" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>1396</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>292</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>294</v>
-      </c>
       <c r="C59" s="13" t="s">
-        <v>1215</v>
+        <v>1202</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>1397</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>1216</v>
+        <v>1203</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1565</v>
+        <v>1547</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>1398</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>1217</v>
+        <v>1204</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1566</v>
+        <v>1548</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>1399</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>1218</v>
+        <v>1205</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>1400</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
+        <v>301</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="C63" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="D63" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="E63" s="3" t="s">
-        <v>1376</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>1219</v>
+        <v>1206</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1567</v>
+        <v>1549</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>1401</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>307</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="C65" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="D65" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>311</v>
-      </c>
       <c r="E65" s="3" t="s">
-        <v>1378</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>1220</v>
+        <v>1207</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1568</v>
+        <v>1550</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>1402</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>664</v>
+        <v>1652</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>1221</v>
+        <v>1653</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1569</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>1403</v>
+        <v>1654</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>1655</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>580</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>581</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>1355</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>663</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>665</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="B69" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>668</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>669</v>
-      </c>
       <c r="E69" s="3" t="s">
-        <v>1404</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>1222</v>
+        <v>1208</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1570</v>
+        <v>1551</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>1405</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>1223</v>
+        <v>1209</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1571</v>
+        <v>1552</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>1406</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>1224</v>
+        <v>1210</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>1407</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>1225</v>
+        <v>1211</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>1408</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>1226</v>
+        <v>1212</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1572</v>
+        <v>1553</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>1409</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>1227</v>
+        <v>1213</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>1410</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>1228</v>
+        <v>1214</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1573</v>
+        <v>1554</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>1411</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>1229</v>
+        <v>1215</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>1574</v>
+        <v>1555</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>1412</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>1230</v>
+        <v>1216</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1575</v>
+        <v>1556</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>1413</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>1231</v>
+        <v>1217</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1576</v>
+        <v>1557</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>1414</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>1232</v>
+        <v>1218</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1577</v>
+        <v>1558</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>1415</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>133</v>
@@ -13604,148 +13541,148 @@
         <v>135</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>1416</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>138</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>1233</v>
+        <v>1219</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>140</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>1417</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>1234</v>
+        <v>1220</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1578</v>
+        <v>1559</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>1418</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>1235</v>
+        <v>1221</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1579</v>
+        <v>1560</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>1419</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>695</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>697</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>699</v>
-      </c>
-      <c r="C85" s="13" t="s">
-        <v>700</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>701</v>
-      </c>
       <c r="E85" s="3" t="s">
-        <v>1420</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>1236</v>
+        <v>1222</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1580</v>
+        <v>1561</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>1421</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>1237</v>
+        <v>1223</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1581</v>
+        <v>1562</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>1422</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>1238</v>
+        <v>1224</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1582</v>
+        <v>1563</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1423</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>312</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B89" s="4" t="s">
-        <v>314</v>
-      </c>
       <c r="C89" s="15" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1070</v>
+        <v>1059</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>1004</v>
+        <v>994</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>128</v>
@@ -13757,63 +13694,63 @@
         <v>130</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>1424</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
+        <v>315</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>317</v>
-      </c>
       <c r="C91" s="15" t="s">
-        <v>1239</v>
+        <v>1225</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>1005</v>
+        <v>995</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>1240</v>
+        <v>1226</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>75</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>1425</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
+        <v>321</v>
+      </c>
+      <c r="B93" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B93" s="4" t="s">
-        <v>323</v>
-      </c>
       <c r="C93" s="15" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>128</v>
@@ -13825,624 +13762,624 @@
         <v>130</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>1424</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
+        <v>707</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>712</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>713</v>
-      </c>
       <c r="E95" s="3" t="s">
-        <v>1426</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>1241</v>
+        <v>1227</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1583</v>
+        <v>1564</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>1427</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
+        <v>346</v>
+      </c>
+      <c r="B97" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="B97" s="4" t="s">
-        <v>348</v>
-      </c>
       <c r="C97" s="15" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>1020</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>1242</v>
+        <v>1228</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>1428</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>1200</v>
+        <v>1187</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>1362</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
+        <v>317</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B100" s="4" t="s">
-        <v>319</v>
-      </c>
       <c r="C100" s="15" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
+        <v>319</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B101" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="C101" s="15" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>1243</v>
+        <v>1229</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>1584</v>
+        <v>1565</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>1429</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="C103" s="13" t="s">
-        <v>722</v>
+        <v>1659</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>1660</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>1430</v>
+        <v>1661</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>1662</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
+        <v>325</v>
+      </c>
+      <c r="B104" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B104" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="C104" s="13" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
+        <v>327</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B105" s="4" t="s">
-        <v>329</v>
-      </c>
       <c r="C105" s="13" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>1431</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>1244</v>
+        <v>1230</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>1432</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
+        <v>331</v>
+      </c>
+      <c r="B107" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B107" s="4" t="s">
-        <v>333</v>
-      </c>
       <c r="C107" s="15" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>1072</v>
+        <v>1061</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
+        <v>333</v>
+      </c>
+      <c r="B108" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B108" s="4" t="s">
-        <v>335</v>
-      </c>
       <c r="C108" s="15" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>1014</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
+        <v>336</v>
+      </c>
+      <c r="B110" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="B110" s="4" t="s">
-        <v>338</v>
-      </c>
       <c r="C110" s="15" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>1015</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
+        <v>338</v>
+      </c>
+      <c r="B111" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="B111" s="4" t="s">
-        <v>340</v>
-      </c>
       <c r="C111" s="15" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>1016</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
+        <v>340</v>
+      </c>
+      <c r="B112" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B112" s="4" t="s">
-        <v>342</v>
-      </c>
       <c r="C112" s="15" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>1017</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
+        <v>342</v>
+      </c>
+      <c r="B113" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="B113" s="4" t="s">
-        <v>344</v>
-      </c>
       <c r="C113" s="15" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>1018</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
+        <v>344</v>
+      </c>
+      <c r="B114" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="B114" s="4" t="s">
-        <v>346</v>
-      </c>
       <c r="C114" s="15" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>1019</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1677</v>
+        <v>1648</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>1678</v>
+        <v>1649</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>1679</v>
+        <v>1650</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>1678</v>
+        <v>1649</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>1680</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>1245</v>
+        <v>1231</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>1585</v>
+        <v>1566</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>1433</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>1246</v>
+        <v>1232</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>1586</v>
+        <v>1567</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>1434</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>1247</v>
+        <v>1233</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1587</v>
+        <v>1568</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1435</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>1248</v>
+        <v>1234</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>1588</v>
+        <v>1569</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1436</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>1437</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>1249</v>
+        <v>1235</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>1589</v>
+        <v>1570</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>1438</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>1250</v>
+        <v>1236</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>1439</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>1251</v>
+        <v>1237</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>1590</v>
+        <v>1571</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1440</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>1252</v>
+        <v>1238</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>1591</v>
+        <v>1572</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1441</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>1253</v>
+        <v>1239</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1442</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
+        <v>348</v>
+      </c>
+      <c r="B126" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="B126" s="4" t="s">
-        <v>350</v>
-      </c>
       <c r="C126" s="15" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1021</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
+        <v>350</v>
+      </c>
+      <c r="B127" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="B127" s="4" t="s">
-        <v>352</v>
-      </c>
       <c r="C127" s="15" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1443</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
+        <v>352</v>
+      </c>
+      <c r="B128" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="C128" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="C128" s="13" t="s">
+      <c r="D128" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D128" s="3" t="s">
-        <v>356</v>
-      </c>
       <c r="E128" s="3" t="s">
-        <v>1444</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
+        <v>357</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="C129" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="C129" s="13" t="s">
+      <c r="D129" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>361</v>
-      </c>
       <c r="E129" s="3" t="s">
-        <v>1445</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>169</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>1079</v>
+        <v>1068</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>171</v>
@@ -14454,29 +14391,29 @@
         <v>173</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>1446</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>176</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>1254</v>
+        <v>1240</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>1447</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>181</v>
@@ -14488,12 +14425,12 @@
         <v>183</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>1448</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>186</v>
@@ -14505,46 +14442,46 @@
         <v>188</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>1449</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
+        <v>368</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="B135" s="4" t="s">
-        <v>370</v>
-      </c>
       <c r="C135" s="15" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>1593</v>
+        <v>1574</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
+        <v>370</v>
+      </c>
+      <c r="B136" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="B136" s="4" t="s">
-        <v>372</v>
-      </c>
       <c r="C136" s="15" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>1594</v>
+        <v>1575</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>1025</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>171</v>
@@ -14556,1100 +14493,1100 @@
         <v>173</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>1446</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>1255</v>
+        <v>1241</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>1595</v>
+        <v>1576</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>1450</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>176</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>1254</v>
+        <v>1240</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>1447</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>1256</v>
+        <v>1242</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>1596</v>
+        <v>1577</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>1451</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>1257</v>
+        <v>1243</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>1597</v>
+        <v>1578</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>1452</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>1258</v>
+        <v>1244</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>1598</v>
+        <v>1579</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>1453</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>1259</v>
+        <v>1245</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>1454</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>1169</v>
+        <v>1156</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>1600</v>
+        <v>1581</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>1455</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>1260</v>
+        <v>1246</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>1601</v>
+        <v>1582</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>1456</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
+        <v>372</v>
+      </c>
+      <c r="B146" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="C146" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="C146" s="13" t="s">
+      <c r="D146" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D146" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="E146" s="3" t="s">
-        <v>1457</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>1261</v>
+        <v>1247</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>1602</v>
+        <v>1583</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>1458</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="B148" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C148" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="C148" s="13" t="s">
+      <c r="D148" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="E148" s="3" t="s">
-        <v>1376</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>1262</v>
+        <v>1248</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>1603</v>
+        <v>1584</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>1459</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>1263</v>
+        <v>1249</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>1460</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>1264</v>
+        <v>1250</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>1604</v>
+        <v>1585</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>1461</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>1265</v>
+        <v>1251</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>1605</v>
+        <v>1586</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>1462</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>1122</v>
+        <v>1109</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>1266</v>
+        <v>1252</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>1606</v>
+        <v>1587</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>1463</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>1267</v>
+        <v>1253</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>1607</v>
+        <v>1588</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>1464</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>1268</v>
+        <v>1254</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>1608</v>
+        <v>1589</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>1465</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
+        <v>377</v>
+      </c>
+      <c r="B157" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="B157" s="4" t="s">
-        <v>379</v>
-      </c>
       <c r="C157" s="15" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>1026</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B158" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C158" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="C158" s="13" t="s">
+      <c r="D158" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D158" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="E158" s="3" t="s">
-        <v>1457</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="B159" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C159" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="C159" s="13" t="s">
+      <c r="D159" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D159" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="E159" s="3" t="s">
-        <v>1457</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>1269</v>
+        <v>1255</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>1609</v>
+        <v>1590</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>1466</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>1270</v>
+        <v>1256</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>1610</v>
+        <v>1591</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>1467</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>790</v>
+        <v>1665</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>1271</v>
+        <v>1664</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>1611</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>1468</v>
+        <v>1666</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>1667</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>1118</v>
+        <v>1105</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>1119</v>
+        <v>1106</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>1120</v>
+        <v>1107</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>1121</v>
+        <v>1108</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>1122</v>
+        <v>1109</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>1124</v>
+        <v>1111</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>1272</v>
+        <v>1257</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>1612</v>
+        <v>1592</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>1469</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>1273</v>
+        <v>1258</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>1613</v>
+        <v>1593</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>1470</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>1274</v>
+        <v>1259</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>1614</v>
+        <v>1594</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>1471</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>1121</v>
+        <v>1108</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>1472</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>1275</v>
+        <v>1260</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>1615</v>
+        <v>1595</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>1473</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>1276</v>
+        <v>1261</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>1616</v>
+        <v>1596</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>1474</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>1277</v>
+        <v>1262</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>1617</v>
+        <v>1597</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>1475</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>1126</v>
+        <v>1113</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
+        <v>401</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C181" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="D181" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C181" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>406</v>
-      </c>
       <c r="E181" s="3" t="s">
-        <v>1476</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
+        <v>406</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C182" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="D182" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B182" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="C182" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>410</v>
-      </c>
       <c r="E182" s="3" t="s">
-        <v>1477</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>1127</v>
+        <v>1114</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B184" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C184" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D184" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C184" s="13" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="E184" s="3" t="s">
-        <v>1478</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>1128</v>
+        <v>1115</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>1633</v>
+        <v>1669</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>1636</v>
+        <v>1668</v>
       </c>
       <c r="D186" t="s">
-        <v>1639</v>
+        <v>1619</v>
       </c>
       <c r="E186" t="s">
-        <v>1642</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" ht="16" x14ac:dyDescent="0.4">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>805</v>
-      </c>
-      <c r="B187" s="20" t="s">
-        <v>1634</v>
+        <v>798</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1614</v>
       </c>
       <c r="C187" t="s">
-        <v>1637</v>
+        <v>1617</v>
       </c>
       <c r="D187" t="s">
-        <v>1640</v>
+        <v>1620</v>
       </c>
       <c r="E187" t="s">
-        <v>1643</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C188" s="15" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>1129</v>
+        <v>1116</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C189" s="15" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>1128</v>
+        <v>1115</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>1633</v>
+        <v>1669</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>1636</v>
+        <v>1668</v>
       </c>
       <c r="D190" t="s">
-        <v>1639</v>
+        <v>1619</v>
       </c>
       <c r="E190" t="s">
-        <v>1642</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>930</v>
+        <v>403</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>1036</v>
+        <v>404</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C192" s="15" t="s">
-        <v>931</v>
+        <v>407</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>1037</v>
+        <v>408</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>1128</v>
+        <v>1115</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>1278</v>
+        <v>1263</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>1618</v>
+        <v>1598</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>1479</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>1633</v>
+        <v>1613</v>
       </c>
       <c r="C195" s="15" t="s">
-        <v>1636</v>
+        <v>1616</v>
       </c>
       <c r="D195" t="s">
-        <v>1639</v>
+        <v>1619</v>
       </c>
       <c r="E195" t="s">
-        <v>1642</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>1635</v>
+        <v>1615</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>1638</v>
+        <v>1618</v>
       </c>
       <c r="D196" t="s">
-        <v>1641</v>
+        <v>1621</v>
       </c>
       <c r="E196" t="s">
-        <v>1644</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A197" s="7" t="s">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>1651</v>
+        <v>1626</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>1651</v>
-      </c>
-      <c r="D197" s="9" t="s">
-        <v>1651</v>
-      </c>
-      <c r="E197" s="9" t="s">
-        <v>1651</v>
+        <v>1633</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>1635</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="7" t="s">
-        <v>1654</v>
+        <v>1628</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>1630</v>
+        <v>1610</v>
       </c>
       <c r="C198" s="9" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>1630</v>
+        <v>1637</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>1630</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A199" s="7" t="s">
-        <v>1653</v>
+        <v>1627</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>1657</v>
+        <v>1631</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>1652</v>
+        <v>1638</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>1652</v>
+        <v>1639</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>1652</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="7" t="s">
-        <v>1655</v>
+        <v>1629</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>1656</v>
+        <v>1630</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>1656</v>
+        <v>1641</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>1656</v>
+        <v>1630</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>1656</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E201" s="9" t="s">
         <v>1658</v>
-      </c>
-      <c r="B201" s="9" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C201" s="9" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D201" s="9" t="s">
-        <v>1659</v>
-      </c>
-      <c r="E201" s="9" t="s">
-        <v>1659</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E196" xr:uid="{B01EA010-864B-8746-BF5D-2E469295667F}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -15683,189 +15620,189 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1279</v>
+        <v>1264</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1619</v>
+        <v>1599</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1480</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1280</v>
+        <v>1265</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1620</v>
+        <v>1600</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1481</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>1281</v>
+        <v>1266</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1621</v>
+        <v>1601</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1482</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>1282</v>
+        <v>1267</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1622</v>
+        <v>1602</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1483</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1283</v>
+        <v>1268</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1623</v>
+        <v>1603</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1484</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1284</v>
+        <v>1269</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1624</v>
+        <v>1604</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1485</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1285</v>
+        <v>1270</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1625</v>
+        <v>1605</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1486</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1286</v>
+        <v>1271</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1626</v>
+        <v>1606</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1487</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>1287</v>
+        <v>1272</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1627</v>
+        <v>1607</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1488</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1288</v>
+        <v>1273</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1628</v>
+        <v>1608</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1489</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1289</v>
+        <v>1274</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1629</v>
+        <v>1609</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1490</v>
+        <v>1472</v>
       </c>
     </row>
   </sheetData>
@@ -15875,29 +15812,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="5e13aadc-de86-43ee-b386-40c01ba74c80" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07d4ffe0-35c4-4630-b07d-57ff54db67ac">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="3a79588a-61f1-49eb-bf82-c7b2c97b1d12">
-      <UserInfo>
-        <DisplayName>Bravo, Ms. Pamela (WDC)</DisplayName>
-        <AccountId>180</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Silva, Ms. Octavia  (WDC)</DisplayName>
-        <AccountId>212</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -15906,7 +15820,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004BF2CC58B4B21249B9847CAE6C292121" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="20382285bea758b172f195e70f01161d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="07d4ffe0-35c4-4630-b07d-57ff54db67ac" xmlns:ns3="3a79588a-61f1-49eb-bf82-c7b2c97b1d12" xmlns:ns4="5e13aadc-de86-43ee-b386-40c01ba74c80" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d6472e07e44c21502ea15ef197acea5c" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="07d4ffe0-35c4-4630-b07d-57ff54db67ac"/>
@@ -16160,25 +16074,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B9D65FF-F2FD-4C20-A5A5-187B450DED94}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="07d4ffe0-35c4-4630-b07d-57ff54db67ac"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="5e13aadc-de86-43ee-b386-40c01ba74c80"/>
-    <ds:schemaRef ds:uri="3a79588a-61f1-49eb-bf82-c7b2c97b1d12"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="5e13aadc-de86-43ee-b386-40c01ba74c80" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07d4ffe0-35c4-4630-b07d-57ff54db67ac">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="3a79588a-61f1-49eb-bf82-c7b2c97b1d12">
+      <UserInfo>
+        <DisplayName>Bravo, Ms. Pamela (WDC)</DisplayName>
+        <AccountId>180</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Silva, Ms. Octavia  (WDC)</DisplayName>
+        <AccountId>212</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F89B1EF0-638A-46E6-AC33-5AA4149722BE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -16186,7 +16105,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E63CBD55-76B1-4172-879F-D383FAB08852}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16204,4 +16123,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B9D65FF-F2FD-4C20-A5A5-187B450DED94}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="07d4ffe0-35c4-4630-b07d-57ff54db67ac"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="5e13aadc-de86-43ee-b386-40c01ba74c80"/>
+    <ds:schemaRef ds:uri="3a79588a-61f1-49eb-bf82-c7b2c97b1d12"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/R/translations.xlsx
+++ b/src/R/translations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5aee5c5b004427f/Documents/mr-risk-assessment/src/R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{132F1232-AAEB-42DF-9114-B0462C5F7248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BECB1E7C-0063-4013-8909-EA7982EEF09C}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{132F1232-AAEB-42DF-9114-B0462C5F7248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0425AC4-2711-4C56-9AAA-630FC2902BBB}"/>
   <bookViews>
-    <workbookView xWindow="110" yWindow="110" windowWidth="19180" windowHeight="10060" xr2:uid="{41A3C097-9B5C-484B-88DA-6A6C7D19F152}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{41A3C097-9B5C-484B-88DA-6A6C7D19F152}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="MSG" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DASHBOARD!$A$1:$E$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DASHBOARD!$A$1:$E$197</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MSG!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">QA_REPORT!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">REPORT!$A$1:$E$170</definedName>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2310" uniqueCount="1674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="1679">
   <si>
     <t>LABEL</t>
   </si>
@@ -2353,9 +2353,6 @@
     <t>thre_vul</t>
   </si>
   <si>
-    <t>Vulnerabilidad</t>
-  </si>
-  <si>
     <t>thre_risk_level</t>
   </si>
   <si>
@@ -2727,9 +2724,6 @@
     <t>Risk assessment for rapid response to imported cases</t>
   </si>
   <si>
-    <t>Presence of trained rapid response team at subnational level</t>
-  </si>
-  <si>
     <t>Appendix: Global variables</t>
   </si>
   <si>
@@ -4908,9 +4902,6 @@
     <t>Penta1-MMR1 drop-out rate</t>
   </si>
   <si>
-    <t>Vulnerability</t>
-  </si>
-  <si>
     <t>Migrant population</t>
   </si>
   <si>
@@ -6443,18 +6434,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Vulnérabilité</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Populations migrantes</t>
     </r>
   </si>
@@ -7050,9 +7029,6 @@
     <t>Taxa de abandono de Penta1-SCR1 (Pontuação)</t>
   </si>
   <si>
-    <t>Vulnerabilidade</t>
-  </si>
-  <si>
     <t>População migrante</t>
   </si>
   <si>
@@ -7152,36 +7128,24 @@
     <t>Equipo capacitado en los últimos 2 años</t>
   </si>
   <si>
-    <t>Areas subnacionales con un equipo que ha sido capacitado en respuesta a brotes en los últimos 2 años</t>
-  </si>
-  <si>
     <t>Presencia de un equipo capacitado en los últimos 2 años (Puntaje)</t>
   </si>
   <si>
     <t>Trained team in the last 2 years</t>
   </si>
   <si>
-    <t>Subnational areas with a team that has been trained in outbreak response in the last 2 years</t>
-  </si>
-  <si>
     <t>Presence of a trained team in the last 2 years (Score)</t>
   </si>
   <si>
     <t>Equipe treinada nos últimos 2 anos</t>
   </si>
   <si>
-    <t>Áreas subnacionais com uma equipe que foi treinada para resposta a surtos nos últimos 2 anos</t>
-  </si>
-  <si>
     <t>Presença de uma equipe treinada nos últimos 2 anos (Pontuação)</t>
   </si>
   <si>
     <t>Équipe formée au cours des 2 dernières années</t>
   </si>
   <si>
-    <t>Zones infranationales avec une équipe formée pour répondre aux épidémies au cours des 2 dernières années</t>
-  </si>
-  <si>
     <t>Présence d'une équipe formée au cours des 2 dernières années (Score)</t>
   </si>
   <si>
@@ -7302,18 +7266,6 @@
     <t>Municipalities reporting cases</t>
   </si>
   <si>
-    <t>Vulnerability by vulnerable groups</t>
-  </si>
-  <si>
-    <t>Vulnerabilidad por grupos vulnerables</t>
-  </si>
-  <si>
-    <t>Vulnerabilidade por grupos vulneráveis</t>
-  </si>
-  <si>
-    <t>Vulnérabilité par groupes vulnérables</t>
-  </si>
-  <si>
     <t>Teams trained in the last 2 years</t>
   </si>
   <si>
@@ -7330,6 +7282,60 @@
   </si>
   <si>
     <t>Vulnerabilité pour les groupes vulnérables</t>
+  </si>
+  <si>
+    <t>Teams trained in outbreak response by subnational level in the last two years</t>
+  </si>
+  <si>
+    <t>Equipes treinadas em resposta a surtos pelo nível subnacional nos últimos dois anos</t>
+  </si>
+  <si>
+    <t>Équipes formées à la riposte aux épidémies par le niveau infranational au cours des deux dernières années</t>
+  </si>
+  <si>
+    <t>Equipos capacitados en respuesta a brotes por el nivel subnacional en los últimos dos años</t>
+  </si>
+  <si>
+    <t>Presence of trained rapid response team at the subnational level</t>
+  </si>
+  <si>
+    <t>Municipalities reporting measles and rubella cases</t>
+  </si>
+  <si>
+    <t>Municípios notificando casos de sarampo e rubéola</t>
+  </si>
+  <si>
+    <t>Municipalités signalant des cas de rougeole et de rubéole</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Municipios notificando casos de sarampión y rubeola</t>
+  </si>
+  <si>
+    <t>rap_pres_team_note</t>
+  </si>
+  <si>
+    <t>Subnational areas with teams trained in outbreak response</t>
+  </si>
+  <si>
+    <t>Áreas subnacionais com equipes treinadas em resposta a surtos</t>
+  </si>
+  <si>
+    <t>Zones infranationales avec des équipes formées à la riposte aux épidémies</t>
+  </si>
+  <si>
+    <t>Áreas subnacionales con equipos capacitados en respuesta a brotes</t>
+  </si>
+  <si>
+    <t>Áreas subnacionales con equipos capacitados en respuesta a brotes en los últimos 2 años</t>
+  </si>
+  <si>
+    <t>Subnational areas with teams trained in outbreak response in the last two years</t>
+  </si>
+  <si>
+    <t>Áreas subnacionais com equipes treinadas em resposta a surtos nos últimos 2 anos</t>
+  </si>
+  <si>
+    <t>Zones infranationales avec des équipes formées à la riposte aux épidémies des 2 dernières années</t>
   </si>
 </sst>
 </file>
@@ -7992,13 +7998,13 @@
         <v>26</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -8009,13 +8015,13 @@
         <v>28</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -8026,13 +8032,13 @@
         <v>30</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -8043,13 +8049,13 @@
         <v>32</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -8060,13 +8066,13 @@
         <v>34</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -8077,13 +8083,13 @@
         <v>36</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="108.5" x14ac:dyDescent="0.35">
@@ -8094,13 +8100,13 @@
         <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="139.5" x14ac:dyDescent="0.35">
@@ -8108,16 +8114,16 @@
         <v>39</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -8199,10 +8205,10 @@
         <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -8213,13 +8219,13 @@
         <v>63</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -8230,13 +8236,13 @@
         <v>65</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -8247,13 +8253,13 @@
         <v>67</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -8264,13 +8270,13 @@
         <v>69</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -8281,13 +8287,13 @@
         <v>71</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -8315,13 +8321,13 @@
         <v>78</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -8332,13 +8338,13 @@
         <v>80</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="108.5" x14ac:dyDescent="0.35">
@@ -8349,13 +8355,13 @@
         <v>82</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="139.5" x14ac:dyDescent="0.35">
@@ -8366,13 +8372,13 @@
         <v>84</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="93" x14ac:dyDescent="0.35">
@@ -8380,16 +8386,16 @@
         <v>85</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="62" x14ac:dyDescent="0.35">
@@ -8400,13 +8406,13 @@
         <v>87</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="93" x14ac:dyDescent="0.35">
@@ -8417,13 +8423,13 @@
         <v>89</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="220" customHeight="1" x14ac:dyDescent="0.35">
@@ -8434,13 +8440,13 @@
         <v>91</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -8451,13 +8457,13 @@
         <v>93</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -8468,7 +8474,7 @@
         <v>95</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>95</v>
@@ -8488,10 +8494,10 @@
         <v>96</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -8502,13 +8508,13 @@
         <v>99</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>99</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -8519,7 +8525,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>101</v>
@@ -8536,13 +8542,13 @@
         <v>103</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -8553,13 +8559,13 @@
         <v>105</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -8570,13 +8576,13 @@
         <v>107</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -8587,13 +8593,13 @@
         <v>109</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -8604,13 +8610,13 @@
         <v>111</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -8621,13 +8627,13 @@
         <v>113</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -8638,13 +8644,13 @@
         <v>115</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -8655,13 +8661,13 @@
         <v>117</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -8689,13 +8695,13 @@
         <v>124</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8706,13 +8712,13 @@
         <v>126</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -8791,13 +8797,13 @@
         <v>148</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -8808,13 +8814,13 @@
         <v>150</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -8825,13 +8831,13 @@
         <v>152</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="77.5" x14ac:dyDescent="0.35">
@@ -8842,13 +8848,13 @@
         <v>154</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -8859,13 +8865,13 @@
         <v>156</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
@@ -8876,13 +8882,13 @@
         <v>158</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -8893,30 +8899,30 @@
         <v>160</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="B60" s="9" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>1626</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>1633</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>1634</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>1635</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
@@ -8944,13 +8950,13 @@
         <v>167</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.35">
@@ -8961,13 +8967,13 @@
         <v>169</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -9063,13 +9069,13 @@
         <v>196</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -9080,13 +9086,13 @@
         <v>198</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -9097,13 +9103,13 @@
         <v>200</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -9111,16 +9117,16 @@
         <v>201</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1665</v>
+        <v>413</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>1664</v>
+        <v>1157</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1666</v>
+        <v>415</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>1667</v>
+        <v>416</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -9131,13 +9137,13 @@
         <v>203</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
@@ -9148,13 +9154,13 @@
         <v>205</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
@@ -9165,13 +9171,13 @@
         <v>207</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -9182,30 +9188,30 @@
         <v>209</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>876</v>
+        <v>1665</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>210</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C77" s="15" t="s">
-        <v>1668</v>
+      <c r="B77" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1661</v>
       </c>
       <c r="D77" t="s">
-        <v>1619</v>
+        <v>1662</v>
       </c>
       <c r="E77" t="s">
-        <v>1622</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
@@ -9216,13 +9222,13 @@
         <v>212</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
@@ -9233,13 +9239,13 @@
         <v>214</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
@@ -9250,13 +9256,13 @@
         <v>216</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>216</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
@@ -9267,13 +9273,13 @@
         <v>218</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
@@ -9301,13 +9307,13 @@
         <v>225</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
@@ -9318,13 +9324,13 @@
         <v>227</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
@@ -9369,13 +9375,13 @@
         <v>239</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
@@ -9403,13 +9409,13 @@
         <v>245</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>245</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
@@ -9420,13 +9426,13 @@
         <v>247</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
@@ -9437,13 +9443,13 @@
         <v>249</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
@@ -9454,13 +9460,13 @@
         <v>251</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
@@ -9471,13 +9477,13 @@
         <v>245</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>245</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
@@ -9488,13 +9494,13 @@
         <v>216</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>216</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
@@ -9505,13 +9511,13 @@
         <v>255</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>255</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
@@ -9522,13 +9528,13 @@
         <v>257</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
@@ -9539,13 +9545,13 @@
         <v>259</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
@@ -9556,13 +9562,13 @@
         <v>261</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
@@ -9573,13 +9579,13 @@
         <v>263</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="17.5" x14ac:dyDescent="0.35">
@@ -9590,13 +9596,13 @@
         <v>265</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
@@ -9607,13 +9613,13 @@
         <v>255</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>255</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
@@ -9624,13 +9630,13 @@
         <v>216</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>216</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
@@ -9862,13 +9868,13 @@
         <v>313</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D116" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
@@ -9896,13 +9902,13 @@
         <v>316</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
@@ -9913,13 +9919,13 @@
         <v>318</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D119" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
@@ -9930,13 +9936,13 @@
         <v>320</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D120" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
@@ -9947,13 +9953,13 @@
         <v>322</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D121" t="s">
         <v>322</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
@@ -9964,13 +9970,13 @@
         <v>324</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D122" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
@@ -9987,7 +9993,7 @@
         <v>719</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
@@ -9998,13 +10004,13 @@
         <v>328</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D124" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -10015,13 +10021,13 @@
         <v>330</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
@@ -10032,13 +10038,13 @@
         <v>332</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D126" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
@@ -10049,13 +10055,13 @@
         <v>334</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D127" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
@@ -10066,13 +10072,13 @@
         <v>320</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D128" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
@@ -10083,13 +10089,13 @@
         <v>337</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D129" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
@@ -10100,13 +10106,13 @@
         <v>339</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D130" t="s">
         <v>339</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
@@ -10117,13 +10123,13 @@
         <v>341</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D131" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -10134,13 +10140,13 @@
         <v>343</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
@@ -10151,13 +10157,13 @@
         <v>345</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D133" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
@@ -10168,13 +10174,13 @@
         <v>347</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D134" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
@@ -10185,13 +10191,13 @@
         <v>349</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D135" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
@@ -10202,13 +10208,13 @@
         <v>351</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D136" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
@@ -10253,13 +10259,13 @@
         <v>363</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
@@ -10338,13 +10344,13 @@
         <v>369</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>173</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
@@ -10355,13 +10361,13 @@
         <v>371</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
@@ -10389,13 +10395,13 @@
         <v>378</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D147" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
@@ -10420,16 +10426,16 @@
         <v>380</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>1670</v>
+        <v>1657</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>1671</v>
+        <v>1658</v>
       </c>
       <c r="D149" t="s">
-        <v>1672</v>
+        <v>1659</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>1673</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
@@ -10440,13 +10446,13 @@
         <v>382</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D150" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
@@ -10457,13 +10463,13 @@
         <v>384</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D151" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
@@ -10474,13 +10480,13 @@
         <v>386</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
@@ -10491,13 +10497,13 @@
         <v>388</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D153" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
@@ -10508,13 +10514,13 @@
         <v>390</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D154" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
@@ -10525,13 +10531,13 @@
         <v>392</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D155" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
@@ -10542,13 +10548,13 @@
         <v>394</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="D156" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
@@ -10559,13 +10565,13 @@
         <v>396</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D157" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
@@ -10576,13 +10582,13 @@
         <v>398</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="D158" t="s">
         <v>398</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
@@ -10593,13 +10599,13 @@
         <v>400</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D159" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
@@ -10644,13 +10650,13 @@
         <v>411</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="D162" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
@@ -10678,13 +10684,13 @@
         <v>418</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D164" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
@@ -10692,16 +10698,16 @@
         <v>419</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>1669</v>
+        <v>1656</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>1668</v>
+        <v>1655</v>
       </c>
       <c r="D165" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
       <c r="E165" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
@@ -10712,13 +10718,13 @@
         <v>421</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D166" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
@@ -10729,13 +10735,13 @@
         <v>421</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D167" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
@@ -10743,16 +10749,16 @@
         <v>423</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>1669</v>
+        <v>1656</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>1668</v>
+        <v>1655</v>
       </c>
       <c r="D168" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
       <c r="E168" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
@@ -10789,113 +10795,114 @@
         <v>409</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
-        <v>1625</v>
+        <v>1616</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>1626</v>
+        <v>1669</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>1633</v>
+        <v>1666</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>1634</v>
+        <v>1667</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>1635</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B172" s="9" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C172" s="9" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D172" s="9" t="s">
         <v>1628</v>
       </c>
-      <c r="B172" s="9" t="s">
-        <v>1610</v>
-      </c>
-      <c r="C172" s="9" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D172" s="9" t="s">
-        <v>1637</v>
-      </c>
       <c r="E172" s="9" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
-        <v>1627</v>
+        <v>1618</v>
       </c>
       <c r="B173" s="9" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C173" s="9" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>1630</v>
+      </c>
+      <c r="E173" s="9" t="s">
         <v>1631</v>
-      </c>
-      <c r="C173" s="9" t="s">
-        <v>1638</v>
-      </c>
-      <c r="D173" s="9" t="s">
-        <v>1639</v>
-      </c>
-      <c r="E173" s="9" t="s">
-        <v>1640</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
-        <v>1629</v>
+        <v>1620</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>1630</v>
+        <v>1621</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>1641</v>
+        <v>1632</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>1630</v>
+        <v>1621</v>
       </c>
       <c r="E174" s="9" t="s">
-        <v>1642</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
-        <v>1632</v>
+        <v>1623</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>1656</v>
+        <v>1647</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>1657</v>
+        <v>1648</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>1658</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
-        <v>1643</v>
+        <v>1634</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>1644</v>
+        <v>1635</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>1645</v>
+        <v>1636</v>
       </c>
       <c r="D176" s="9" t="s">
-        <v>1646</v>
+        <v>1637</v>
       </c>
       <c r="E176" s="9" t="s">
-        <v>1647</v>
+        <v>1638</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E170" xr:uid="{064C7D9D-C4E2-B94C-B003-B8DCE10597B7}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -10934,13 +10941,13 @@
         <v>427</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -10951,13 +10958,13 @@
         <v>429</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -11005,7 +11012,7 @@
         <v>433</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>433</v>
@@ -11019,13 +11026,13 @@
         <v>435</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -11053,13 +11060,13 @@
         <v>439</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -11070,13 +11077,13 @@
         <v>441</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -11087,13 +11094,13 @@
         <v>443</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11104,13 +11111,13 @@
         <v>445</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -11121,13 +11128,13 @@
         <v>447</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11138,13 +11145,13 @@
         <v>449</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11155,13 +11162,13 @@
         <v>451</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -11172,13 +11179,13 @@
         <v>453</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -11189,13 +11196,13 @@
         <v>455</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -11206,13 +11213,13 @@
         <v>457</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -11223,13 +11230,13 @@
         <v>459</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -11240,13 +11247,13 @@
         <v>461</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -11257,13 +11264,13 @@
         <v>463</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -11274,13 +11281,13 @@
         <v>465</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>465</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -11291,13 +11298,13 @@
         <v>467</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -11308,13 +11315,13 @@
         <v>469</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -11325,13 +11332,13 @@
         <v>471</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -11342,13 +11349,13 @@
         <v>473</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -11359,13 +11366,13 @@
         <v>475</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -11376,13 +11383,13 @@
         <v>477</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -11396,10 +11403,10 @@
         <v>479</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -11410,13 +11417,13 @@
         <v>481</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -11427,13 +11434,13 @@
         <v>483</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -11444,13 +11451,13 @@
         <v>485</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11461,13 +11468,13 @@
         <v>487</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11478,13 +11485,13 @@
         <v>489</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11495,13 +11502,13 @@
         <v>491</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -11512,13 +11519,13 @@
         <v>493</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
@@ -11529,13 +11536,13 @@
         <v>495</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
@@ -11546,13 +11553,13 @@
         <v>497</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -11563,13 +11570,13 @@
         <v>499</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -11580,7 +11587,7 @@
         <v>501</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>121</v>
@@ -11631,13 +11638,13 @@
         <v>507</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11648,13 +11655,13 @@
         <v>509</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -11665,13 +11672,13 @@
         <v>511</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -11682,7 +11689,7 @@
         <v>162</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>164</v>
@@ -11699,13 +11706,13 @@
         <v>514</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -11716,13 +11723,13 @@
         <v>516</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11733,13 +11740,13 @@
         <v>518</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -11750,7 +11757,7 @@
         <v>413</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>415</v>
@@ -11767,13 +11774,13 @@
         <v>521</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.35">
@@ -11784,13 +11791,13 @@
         <v>523</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
@@ -11801,13 +11808,13 @@
         <v>525</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -11821,7 +11828,7 @@
         <v>433</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>433</v>
@@ -11835,13 +11842,13 @@
         <v>528</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
@@ -11852,13 +11859,13 @@
         <v>530</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11869,13 +11876,13 @@
         <v>532</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11886,13 +11893,13 @@
         <v>534</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
@@ -11903,13 +11910,13 @@
         <v>536</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11920,13 +11927,13 @@
         <v>538</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
@@ -11937,13 +11944,13 @@
         <v>540</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
@@ -11954,13 +11961,13 @@
         <v>542</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11971,13 +11978,13 @@
         <v>544</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -11988,13 +11995,13 @@
         <v>546</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -12005,13 +12012,13 @@
         <v>548</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -12022,13 +12029,13 @@
         <v>550</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1527</v>
+        <v>1523</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -12039,13 +12046,13 @@
         <v>552</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1528</v>
+        <v>1524</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -12056,7 +12063,7 @@
         <v>554</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>612</v>
@@ -12073,13 +12080,13 @@
         <v>556</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -12090,13 +12097,13 @@
         <v>558</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -12107,13 +12114,13 @@
         <v>560</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -12124,13 +12131,13 @@
         <v>562</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -12141,13 +12148,13 @@
         <v>564</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
   </sheetData>
@@ -12159,7 +12166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01EA010-864B-8746-BF5D-2E469295667F}">
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E202"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.5" bestFit="1" customWidth="1"/>
@@ -12198,7 +12205,7 @@
         <v>568</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -12215,7 +12222,7 @@
         <v>572</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -12226,13 +12233,13 @@
         <v>574</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -12249,7 +12256,7 @@
         <v>222</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -12266,7 +12273,7 @@
         <v>579</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -12283,7 +12290,7 @@
         <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -12300,7 +12307,7 @@
         <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -12311,13 +12318,13 @@
         <v>581</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -12328,13 +12335,13 @@
         <v>583</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -12345,13 +12352,13 @@
         <v>585</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -12362,13 +12369,13 @@
         <v>587</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -12379,13 +12386,13 @@
         <v>589</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>589</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -12396,13 +12403,13 @@
         <v>591</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -12419,7 +12426,7 @@
         <v>594</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -12436,7 +12443,7 @@
         <v>598</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -12447,13 +12454,13 @@
         <v>601</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1540</v>
+        <v>1536</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -12464,13 +12471,13 @@
         <v>603</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>603</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -12481,13 +12488,13 @@
         <v>605</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>606</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -12498,13 +12505,13 @@
         <v>119</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -12515,13 +12522,13 @@
         <v>143</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -12532,13 +12539,13 @@
         <v>162</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>164</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -12549,13 +12556,13 @@
         <v>191</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>193</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -12566,13 +12573,13 @@
         <v>554</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>612</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -12583,13 +12590,13 @@
         <v>605</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>606</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -12600,13 +12607,13 @@
         <v>119</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -12617,13 +12624,13 @@
         <v>143</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>145</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -12634,13 +12641,13 @@
         <v>162</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>164</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -12651,13 +12658,13 @@
         <v>191</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>193</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -12668,13 +12675,13 @@
         <v>554</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>612</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -12691,7 +12698,7 @@
         <v>623</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -12708,7 +12715,7 @@
         <v>579</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -12719,13 +12726,13 @@
         <v>626</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -12742,7 +12749,7 @@
         <v>304</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -12753,13 +12760,13 @@
         <v>629</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -12776,7 +12783,7 @@
         <v>304</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -12793,7 +12800,7 @@
         <v>310</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -12804,13 +12811,13 @@
         <v>633</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -12821,13 +12828,13 @@
         <v>635</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>635</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -12838,13 +12845,13 @@
         <v>637</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>637</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -12855,13 +12862,13 @@
         <v>639</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -12872,13 +12879,13 @@
         <v>641</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -12895,7 +12902,7 @@
         <v>642</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -12912,7 +12919,7 @@
         <v>646</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -12923,13 +12930,13 @@
         <v>26</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -12946,7 +12953,7 @@
         <v>43</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -12963,7 +12970,7 @@
         <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -12980,7 +12987,7 @@
         <v>53</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -12997,7 +13004,7 @@
         <v>58</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -13008,13 +13015,13 @@
         <v>648</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -13028,10 +13035,10 @@
         <v>96</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -13045,10 +13052,10 @@
         <v>60</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
@@ -13059,13 +13066,13 @@
         <v>71</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -13082,7 +13089,7 @@
         <v>271</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
@@ -13099,7 +13106,7 @@
         <v>651</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
@@ -13116,7 +13123,7 @@
         <v>281</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -13133,7 +13140,7 @@
         <v>286</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
@@ -13150,7 +13157,7 @@
         <v>289</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
@@ -13161,13 +13168,13 @@
         <v>293</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>295</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -13178,13 +13185,13 @@
         <v>653</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
@@ -13195,13 +13202,13 @@
         <v>655</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
@@ -13212,13 +13219,13 @@
         <v>657</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>657</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
@@ -13235,7 +13242,7 @@
         <v>304</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -13246,13 +13253,13 @@
         <v>658</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1549</v>
+        <v>1545</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -13269,7 +13276,7 @@
         <v>310</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -13280,13 +13287,13 @@
         <v>660</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -13294,16 +13301,16 @@
         <v>661</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1652</v>
+        <v>1643</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>1653</v>
+        <v>1644</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1654</v>
+        <v>1645</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>1655</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -13320,7 +13327,7 @@
         <v>579</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -13337,7 +13344,7 @@
         <v>666</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -13348,13 +13355,13 @@
         <v>668</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1551</v>
+        <v>1547</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -13365,13 +13372,13 @@
         <v>670</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1552</v>
+        <v>1548</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -13382,13 +13389,13 @@
         <v>672</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>672</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -13399,13 +13406,13 @@
         <v>674</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>674</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
@@ -13416,13 +13423,13 @@
         <v>676</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1553</v>
+        <v>1549</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
@@ -13433,13 +13440,13 @@
         <v>678</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>678</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
@@ -13450,13 +13457,13 @@
         <v>680</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1554</v>
+        <v>1550</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
@@ -13467,13 +13474,13 @@
         <v>682</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
@@ -13484,13 +13491,13 @@
         <v>684</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1556</v>
+        <v>1552</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
@@ -13501,13 +13508,13 @@
         <v>686</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
@@ -13518,13 +13525,13 @@
         <v>688</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1558</v>
+        <v>1554</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
@@ -13541,7 +13548,7 @@
         <v>135</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
@@ -13552,13 +13559,13 @@
         <v>138</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>140</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
@@ -13569,13 +13576,13 @@
         <v>692</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
@@ -13586,13 +13593,13 @@
         <v>694</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
@@ -13609,7 +13616,7 @@
         <v>698</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
@@ -13620,13 +13627,13 @@
         <v>700</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
@@ -13637,13 +13644,13 @@
         <v>702</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
@@ -13654,13 +13661,13 @@
         <v>704</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1563</v>
+        <v>1559</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -13671,13 +13678,13 @@
         <v>313</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -13694,7 +13701,7 @@
         <v>130</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -13705,13 +13712,13 @@
         <v>316</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
@@ -13722,13 +13729,13 @@
         <v>73</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>75</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
@@ -13739,13 +13746,13 @@
         <v>322</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>322</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -13762,7 +13769,7 @@
         <v>130</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -13779,7 +13786,7 @@
         <v>710</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
@@ -13790,13 +13797,13 @@
         <v>712</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1564</v>
+        <v>1560</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
@@ -13807,13 +13814,13 @@
         <v>347</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
@@ -13824,13 +13831,13 @@
         <v>714</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>714</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
@@ -13841,13 +13848,13 @@
         <v>589</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>589</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
@@ -13858,13 +13865,13 @@
         <v>318</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
@@ -13875,13 +13882,13 @@
         <v>320</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
@@ -13892,13 +13899,13 @@
         <v>717</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -13906,16 +13913,16 @@
         <v>323</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>1659</v>
+        <v>1650</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>1660</v>
+        <v>1651</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1661</v>
+        <v>1652</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>1662</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
@@ -13932,7 +13939,7 @@
         <v>719</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
@@ -13943,13 +13950,13 @@
         <v>328</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>720</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -13960,13 +13967,13 @@
         <v>721</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -13977,13 +13984,13 @@
         <v>332</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
@@ -13994,13 +14001,13 @@
         <v>334</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
@@ -14011,13 +14018,13 @@
         <v>320</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
@@ -14028,13 +14035,13 @@
         <v>337</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
@@ -14045,13 +14052,13 @@
         <v>339</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>339</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
@@ -14062,13 +14069,13 @@
         <v>341</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -14079,13 +14086,13 @@
         <v>343</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
@@ -14096,30 +14103,30 @@
         <v>345</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1648</v>
+        <v>1639</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>1649</v>
+        <v>1640</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>1650</v>
+        <v>1641</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>1649</v>
+        <v>1640</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>1651</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
@@ -14130,13 +14137,13 @@
         <v>723</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
@@ -14147,13 +14154,13 @@
         <v>725</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -14164,13 +14171,13 @@
         <v>727</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
@@ -14181,13 +14188,13 @@
         <v>729</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
@@ -14204,7 +14211,7 @@
         <v>733</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
@@ -14215,13 +14222,13 @@
         <v>735</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
@@ -14232,13 +14239,13 @@
         <v>737</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>738</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -14249,13 +14256,13 @@
         <v>740</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -14266,13 +14273,13 @@
         <v>742</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -14283,13 +14290,13 @@
         <v>744</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
@@ -14300,13 +14307,13 @@
         <v>349</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
@@ -14317,13 +14324,13 @@
         <v>351</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
@@ -14340,7 +14347,7 @@
         <v>355</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
@@ -14357,7 +14364,7 @@
         <v>360</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -14368,13 +14375,13 @@
         <v>169</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
@@ -14391,7 +14398,7 @@
         <v>173</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
@@ -14402,13 +14409,13 @@
         <v>176</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
@@ -14425,7 +14432,7 @@
         <v>183</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
@@ -14442,7 +14449,7 @@
         <v>188</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
@@ -14453,13 +14460,13 @@
         <v>369</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
@@ -14470,13 +14477,13 @@
         <v>371</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
@@ -14493,7 +14500,7 @@
         <v>173</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
@@ -14504,13 +14511,13 @@
         <v>747</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>1576</v>
+        <v>1572</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
@@ -14521,13 +14528,13 @@
         <v>176</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
@@ -14538,13 +14545,13 @@
         <v>750</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>1577</v>
+        <v>1573</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
@@ -14555,13 +14562,13 @@
         <v>752</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>1578</v>
+        <v>1574</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
@@ -14572,13 +14579,13 @@
         <v>754</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
@@ -14589,13 +14596,13 @@
         <v>756</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
@@ -14606,13 +14613,13 @@
         <v>758</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
@@ -14623,13 +14630,13 @@
         <v>760</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
@@ -14646,7 +14653,7 @@
         <v>375</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
@@ -14654,21 +14661,21 @@
         <v>761</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>762</v>
+        <v>413</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>1247</v>
+        <v>1157</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>1583</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>1441</v>
+        <v>415</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>302</v>
@@ -14680,143 +14687,143 @@
         <v>304</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
+        <v>763</v>
+      </c>
+      <c r="B149" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="B149" s="4" t="s">
-        <v>765</v>
-      </c>
       <c r="C149" s="15" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
+        <v>765</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="B150" s="4" t="s">
-        <v>767</v>
-      </c>
       <c r="C150" s="15" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
+        <v>767</v>
+      </c>
+      <c r="B151" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="B151" s="4" t="s">
-        <v>769</v>
-      </c>
       <c r="C151" s="15" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
+        <v>769</v>
+      </c>
+      <c r="B152" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="B152" s="4" t="s">
-        <v>771</v>
-      </c>
       <c r="C152" s="15" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>390</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
+        <v>772</v>
+      </c>
+      <c r="B154" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="B154" s="4" t="s">
-        <v>774</v>
-      </c>
       <c r="C154" s="15" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
+        <v>774</v>
+      </c>
+      <c r="B155" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="B155" s="4" t="s">
-        <v>776</v>
-      </c>
       <c r="C155" s="15" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
+        <v>776</v>
+      </c>
+      <c r="B156" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="B156" s="4" t="s">
-        <v>778</v>
-      </c>
       <c r="C156" s="15" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -14827,13 +14834,13 @@
         <v>378</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
@@ -14850,12 +14857,12 @@
         <v>375</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>373</v>
@@ -14867,41 +14874,41 @@
         <v>375</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
+        <v>779</v>
+      </c>
+      <c r="B160" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="B160" s="4" t="s">
-        <v>781</v>
-      </c>
       <c r="C160" s="15" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
+        <v>781</v>
+      </c>
+      <c r="B161" s="4" t="s">
         <v>782</v>
       </c>
-      <c r="B161" s="4" t="s">
-        <v>783</v>
-      </c>
       <c r="C161" s="15" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
@@ -14909,16 +14916,16 @@
         <v>380</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>1665</v>
+        <v>413</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>1664</v>
+        <v>1157</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>1666</v>
+        <v>415</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>1667</v>
+        <v>416</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
@@ -14929,13 +14936,13 @@
         <v>382</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
@@ -14946,13 +14953,13 @@
         <v>384</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -14963,13 +14970,13 @@
         <v>386</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
@@ -14980,13 +14987,13 @@
         <v>388</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
@@ -14997,13 +15004,13 @@
         <v>390</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
@@ -15014,13 +15021,13 @@
         <v>392</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
@@ -15031,13 +15038,13 @@
         <v>394</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
@@ -15048,149 +15055,149 @@
         <v>396</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
+        <v>783</v>
+      </c>
+      <c r="B171" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="B171" s="4" t="s">
-        <v>785</v>
-      </c>
       <c r="C171" s="15" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
+        <v>785</v>
+      </c>
+      <c r="B172" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="B172" s="4" t="s">
-        <v>787</v>
-      </c>
       <c r="C172" s="15" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
+        <v>787</v>
+      </c>
+      <c r="B173" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="B173" s="4" t="s">
-        <v>789</v>
-      </c>
       <c r="C173" s="15" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>388</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
+        <v>790</v>
+      </c>
+      <c r="B175" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="B175" s="4" t="s">
-        <v>792</v>
-      </c>
       <c r="C175" s="15" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>392</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
+        <v>793</v>
+      </c>
+      <c r="B177" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="B177" s="4" t="s">
-        <v>795</v>
-      </c>
       <c r="C177" s="15" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
+        <v>795</v>
+      </c>
+      <c r="B178" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="B178" s="4" t="s">
-        <v>797</v>
-      </c>
       <c r="C178" s="15" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
@@ -15201,13 +15208,13 @@
         <v>398</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>398</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
@@ -15218,13 +15225,13 @@
         <v>400</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
@@ -15241,7 +15248,7 @@
         <v>404</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
@@ -15258,7 +15265,7 @@
         <v>408</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
@@ -15269,13 +15276,13 @@
         <v>411</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
@@ -15286,13 +15293,13 @@
         <v>413</v>
       </c>
       <c r="C184" s="13" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>415</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
@@ -15303,13 +15310,13 @@
         <v>418</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
@@ -15317,278 +15324,295 @@
         <v>419</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>1669</v>
+        <v>1656</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>1668</v>
+        <v>1655</v>
       </c>
       <c r="D186" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
       <c r="E186" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>798</v>
+        <v>1670</v>
       </c>
       <c r="B187" t="s">
-        <v>1614</v>
+        <v>1674</v>
       </c>
       <c r="C187" t="s">
-        <v>1617</v>
+        <v>1671</v>
       </c>
       <c r="D187" t="s">
-        <v>1620</v>
+        <v>1672</v>
       </c>
       <c r="E187" t="s">
-        <v>1623</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>420</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="C188" s="15" t="s">
-        <v>925</v>
-      </c>
-      <c r="D188" s="3" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E188" s="3" t="s">
-        <v>1029</v>
+        <v>797</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D188" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1678</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C189" s="15" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>1669</v>
+        <v>418</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>1668</v>
-      </c>
-      <c r="D190" t="s">
-        <v>1619</v>
-      </c>
-      <c r="E190" t="s">
-        <v>1622</v>
+        <v>922</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>1026</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>402</v>
+        <v>1656</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E191" s="4" t="s">
-        <v>405</v>
+        <v>1655</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1614</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C192" s="15" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>799</v>
+        <v>425</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>924</v>
+        <v>407</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E193" s="3" t="s">
-        <v>1028</v>
+        <v>408</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>801</v>
+        <v>418</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>1263</v>
+        <v>922</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>1598</v>
+        <v>1113</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>1461</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
+        <v>799</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="C195" s="15" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>801</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C196" s="15" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D196" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
         <v>802</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B197" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C197" s="15" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D197" t="s">
         <v>1613</v>
       </c>
-      <c r="C195" s="15" t="s">
+      <c r="E197" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A198" s="7" t="s">
         <v>1616</v>
       </c>
-      <c r="D195" t="s">
+      <c r="B198" s="9" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C198" s="9" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A199" s="7" t="s">
         <v>1619</v>
       </c>
-      <c r="E195" t="s">
+      <c r="B199" s="9" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A200" s="7" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B200" s="9" t="s">
         <v>1622</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A196" t="s">
-        <v>803</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>1615</v>
-      </c>
-      <c r="C196" s="15" t="s">
-        <v>1618</v>
-      </c>
-      <c r="D196" t="s">
-        <v>1621</v>
-      </c>
-      <c r="E196" t="s">
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A197" s="7" t="s">
-        <v>1625</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>1626</v>
-      </c>
-      <c r="C197" s="9" t="s">
-        <v>1633</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>1634</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>1635</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A198" s="7" t="s">
-        <v>1628</v>
-      </c>
-      <c r="B198" s="9" t="s">
-        <v>1610</v>
-      </c>
-      <c r="C198" s="9" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D198" s="9" t="s">
-        <v>1637</v>
-      </c>
-      <c r="E198" s="9" t="s">
-        <v>1611</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" ht="31" x14ac:dyDescent="0.35">
-      <c r="A199" s="7" t="s">
-        <v>1627</v>
-      </c>
-      <c r="B199" s="9" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C199" s="9" t="s">
-        <v>1638</v>
-      </c>
-      <c r="D199" s="9" t="s">
-        <v>1639</v>
-      </c>
-      <c r="E199" s="9" t="s">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A200" s="7" t="s">
+      <c r="C200" s="9" t="s">
         <v>1629</v>
-      </c>
-      <c r="B200" s="9" t="s">
-        <v>1630</v>
-      </c>
-      <c r="C200" s="9" t="s">
-        <v>1641</v>
       </c>
       <c r="D200" s="9" t="s">
         <v>1630</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>1642</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C201" s="9" t="s">
         <v>1632</v>
       </c>
-      <c r="B201" s="9" t="s">
-        <v>1656</v>
-      </c>
-      <c r="C201" s="9" t="s">
-        <v>1663</v>
-      </c>
       <c r="D201" s="9" t="s">
-        <v>1657</v>
+        <v>1621</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>1658</v>
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A202" s="7" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>1649</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E196" xr:uid="{B01EA010-864B-8746-BF5D-2E469295667F}"/>
+  <autoFilter ref="A1:E197" xr:uid="{B01EA010-864B-8746-BF5D-2E469295667F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15620,189 +15644,189 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>805</v>
-      </c>
       <c r="C2" s="13" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>805</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>807</v>
-      </c>
       <c r="C3" s="13" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>807</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>809</v>
-      </c>
       <c r="C4" s="13" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>809</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>810</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>811</v>
-      </c>
       <c r="C5" s="13" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>811</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>813</v>
-      </c>
       <c r="C6" s="13" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>813</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>815</v>
-      </c>
       <c r="C7" s="13" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>817</v>
-      </c>
       <c r="C8" s="13" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>817</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>819</v>
-      </c>
       <c r="C9" s="13" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>819</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>821</v>
-      </c>
       <c r="C10" s="13" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>821</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>823</v>
-      </c>
       <c r="C11" s="13" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>823</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>825</v>
-      </c>
       <c r="C12" s="13" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
   </sheetData>
@@ -15812,12 +15836,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="5e13aadc-de86-43ee-b386-40c01ba74c80" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07d4ffe0-35c4-4630-b07d-57ff54db67ac">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="3a79588a-61f1-49eb-bf82-c7b2c97b1d12">
+      <UserInfo>
+        <DisplayName>Bravo, Ms. Pamela (WDC)</DisplayName>
+        <AccountId>180</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Silva, Ms. Octavia  (WDC)</DisplayName>
+        <AccountId>212</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16075,32 +16113,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="5e13aadc-de86-43ee-b386-40c01ba74c80" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07d4ffe0-35c4-4630-b07d-57ff54db67ac">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="3a79588a-61f1-49eb-bf82-c7b2c97b1d12">
-      <UserInfo>
-        <DisplayName>Bravo, Ms. Pamela (WDC)</DisplayName>
-        <AccountId>180</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Silva, Ms. Octavia  (WDC)</DisplayName>
-        <AccountId>212</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F89B1EF0-638A-46E6-AC33-5AA4149722BE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B9D65FF-F2FD-4C20-A5A5-187B450DED94}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="07d4ffe0-35c4-4630-b07d-57ff54db67ac"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="5e13aadc-de86-43ee-b386-40c01ba74c80"/>
+    <ds:schemaRef ds:uri="3a79588a-61f1-49eb-bf82-c7b2c97b1d12"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16126,19 +16160,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B9D65FF-F2FD-4C20-A5A5-187B450DED94}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F89B1EF0-638A-46E6-AC33-5AA4149722BE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="07d4ffe0-35c4-4630-b07d-57ff54db67ac"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="5e13aadc-de86-43ee-b386-40c01ba74c80"/>
-    <ds:schemaRef ds:uri="3a79588a-61f1-49eb-bf82-c7b2c97b1d12"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/src/R/translations.xlsx
+++ b/src/R/translations.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="2921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3075" uniqueCount="3075">
   <si>
     <t>LABEL</t>
   </si>
@@ -8779,6 +8779,468 @@
   </si>
   <si>
     <t xml:space="preserve">Génération du rapport, veuillez patienter...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acerca de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sobre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À propos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lorem ipsum dolor sit amet, consectetur adipiscing elit. Sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_what_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué es?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que é?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qu'est-ce que c'est ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_what_body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sostenibilidad de la eliminación de la poliomielitis, el sarampión y la rubéola en la Región de las Américas requiere un monitoreo continuo del riesgo para orientar acciones de mitigación oportunas y efectivas. Esta sección presenta la visualización conjunta del análisis de riesgo de polio y el de sarampión y rubéola, utilizando el puntaje total y los componentes compartidos de inmunidad poblacional y calidad de la vigilancia. La visualización conjunta del riesgo no genera un puntaje numérico, sino una clasificación cualitativa del riesgo. Los puntajes individuales de cada análisis se presentan como referencia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sustaining the elimination of poliomyelitis, measles, and rubella in the Region of the Americas requires continuous risk monitoring to guide timely and effective mitigation actions. This section presents the joint visualization of the polio risk analysis and the measles and rubella risk analysis, using the total score and the shared components of population immunity and surveillance quality. The joint risk visualization does not generate a numerical score, but rather a qualitative risk classification. The individual scores from each analysis are presented as a reference.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A sustentabilidade da eliminação da poliomielite, do sarampo e da rubéola na Região das Américas requer monitoramento contínuo do risco para orientar ações de mitigação oportunas e eficazes. Esta seção apresenta a visualização conjunta da análise de risco de poliomielite e da análise de risco de sarampo e rubéola, utilizando a pontuação total e os componentes compartilhados de imunidade populacional e qualidade da vigilância. A visualização conjunta do risco não gera uma pontuação numérica, mas sim uma classificação qualitativa do risco. As pontuações individuais de cada análise são apresentadas como referência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pérennisation de l'élimination de la poliomyélite, de la rougeole et de la rubéole dans la Région des Amériques nécessite une surveillance continue du risque afin d'orienter des actions d'atténuation rapides et efficaces. Cette section présente la visualisation conjointe de l'analyse du risque de poliomyélite et de celle du risque de rougeole et de rubéole, en utilisant le score total et les composantes partagées d'immunité de la population et de qualité de la surveillance. La visualisation conjointe du risque ne génère pas de score numérique, mais plutôt une classification qualitative du risque. Les scores individuels de chaque analyse sont présentés à titre de référence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_scale_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuál es la escala de puntaje por análisis?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the scoring scale for each analysis?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qual é a escala de pontuação por análise?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quelle est l'échelle de score par analyse ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_scale_intro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las variables y la categorización del riesgo difieren entre ambos análisis. En la tabla 1, se presentan las categorías de riesgo y las puntuaciones respectivas para cada análisis:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The variables and risk categorization differ between the two analyses. Table 1 presents the risk categories and corresponding scores for each analysis:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As variáveis e a categorização do risco diferem entre as duas análises. Na tabela 1, são apresentadas as categorias de risco e as respectivas pontuações para cada análise:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les variables et la catégorisation du risque diffèrent entre les deux analyses. Le tableau 1 présente les catégories de risque et les scores respectifs pour chaque analyse :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_scale_table_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabla 1: Puntaje de riesgo asignado a nivel de municipio para polio, sarampión y rubeola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1: Risk score assigned at municipality level for polio, measles, and rubella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabela 1: Pontuação de risco atribuída em nível municipal para poliomielite, sarampo e rubéola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableau 1 : Score de risque attribué au niveau municipal pour la poliomyélite, la rougeole et la rubéole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_scale_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La categorización del riesgo para cada uno de los componentes del análisis de sarampión y rubeola se encuentra aquí. Para polio se encuentra aquí.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The risk categorization for each component of the measles and rubella analysis can be found here. For polio, it can be found here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A categorização do risco para cada um dos componentes da análise de sarampo e rubéola encontra-se aqui. Para poliomielite, encontra-se aqui.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La catégorisation du risque pour chacune des composantes de l'analyse de la rougeole et de la rubéole se trouve ici. Pour la poliomyélite, elle se trouve ici.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_matrix_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como se determina o risco conjunto?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_matrix_intro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se considera la categoría de mayor riesgo entre ambos análisis (ver tabla 2). Por ejemplo, si para el municipio X, el análisis de riesgo para polio fue “Alto”, y para sarampión y rubeola “Muy alto”, entonces la clasificación final de dicho municipio será “Muy alto”. Esta categorización se utiliza para el perfil de riesgo general derivado del puntaje total, así como para los componentes de inmunidad poblacional y calidad de la vigilancia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The higher-risk category between both analyses is used (see table 2). For example, if for municipality X, the polio risk analysis was “High” and the measles and rubella analysis was “Very high,” then the final classification for that municipality will be “Very high.” This categorization is used for the general risk profile derived from the total score, as well as for the population immunity and surveillance quality components.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Considera-se a categoria de maior risco entre as duas análises (ver tabela 2). Por exemplo, se para o município X, a análise de risco de poliomielite foi “Alto” e a de sarampo e rubéola foi “Muito alto”, então a classificação final desse município será “Muito alto”. Essa categorização é utilizada para o perfil de risco geral derivado da pontuação total, bem como para os componentes de imunidade populacional e qualidade da vigilância.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La catégorie de risque la plus élevée entre les deux analyses est retenue (voir tableau 2). Par exemple, si pour la municipalité X, l'analyse du risque de poliomyélite était « Élevé » et celle de la rougeole et de la rubéole « Très élevé », alors la classification finale de cette municipalité sera « Très élevé ». Cette catégorisation est utilisée pour le profil de risque général dérivé du score total, ainsi que pour les composantes d'immunité de la population et de qualité de la surveillance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_matrix_table_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabla 2: Visualización conjunta de los resultados del análisis de riesgo polio, sarampión y rubeola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 2: Joint visualization of the polio, measles, and rubella risk analysis results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabela 2: Visualização conjunta dos resultados da análise de risco de poliomielite, sarampo e rubéola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableau 2 : Visualisation conjointe des résultats de l'analyse du risque de poliomyélite, de rougeole et de rubéole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_matrix_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los puntajes numéricos por cada enfermedad no son directamente comparables; sin embargo, las categorías de riesgo permiten una interpretación conjunta de los resultados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The numerical scores for each disease are not directly comparable; however, the risk categories allow for a joint interpretation of the results.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As pontuações numéricas de cada doença não são diretamente comparáveis; no entanto, as categorias de risco permitem uma interpretação conjunta dos resultados.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les scores numériques de chaque maladie ne sont pas directement comparables ; cependant, les catégories de risque permettent une interprétation conjointe des résultats.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_order_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La herramienta mostrará los puntajes individuales obtenidos para sarampión, rubeola y polio, por cada municipio. El orden por defecto que mostrará la herramienta será la suma de los puntajes obtenidos para sarampión, rubeola y polio. Sin embargo, la herramienta permitirá ordenar la relación de municipios, de mayor a menor, ya sea por los puntajes obtenidos por sarampión/rubeola o por polio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The tool will show the individual scores obtained for measles, rubella, and polio for each municipality. The tool's default order will be the sum of the scores obtained for measles, rubella, and polio. However, the tool will allow the list of municipalities to be sorted, from highest to lowest, by either the measles/rubella scores or the polio scores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A ferramenta mostrará as pontuações individuais obtidas para sarampo, rubéola e poliomielite, por município. A ordem padrão exibida pela ferramenta será a soma das pontuações obtidas para sarampo, rubéola e poliomielite. No entanto, a ferramenta permitirá ordenar a lista de municípios, do maior para o menor, seja pelas pontuações obtidas para sarampo/rubéola ou para poliomielite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'outil affichera les scores individuels obtenus pour la rougeole, la rubéole et la poliomyélite, pour chaque municipalité. L'ordre par défaut affiché par l'outil sera la somme des scores obtenus pour la rougeole, la rubéole et la poliomyélite. Toutefois, l'outil permettra de trier la liste des municipalités, du plus élevé au plus faible, selon les scores obtenus pour la rougeole/rubéole ou pour la poliomyélite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_results_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cómo se obtienen los resultados?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How are the results obtained?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como são obtidos os resultados?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment les résultats sont-ils obtenus ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_results_body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se debe realizar el análisis de riesgo para poliomielitis, sarampión y rubéola. A partir de los resultados obtenidos, la herramienta permite integrar y visualizar de manera conjunta y automatizada dichos análisis, presentándolos en un tablero interactivo y en reportes generados en formatos HTML y Word.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The risk analysis for poliomyelitis, measles, and rubella must be carried out. Based on the results obtained, the tool integrates and visualizes these analyses jointly and automatically, presenting them in an interactive dashboard and in reports generated in HTML and Word formats.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deve-se realizar a análise de risco para poliomielite, sarampo e rubéola. A partir dos resultados obtidos, a ferramenta permite integrar e visualizar de forma conjunta e automatizada essas análises, apresentando-as em um painel interativo e em relatórios gerados nos formatos HTML e Word.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'analyse du risque de poliomyélite, de rougeole et de rubéole doit être réalisée. À partir des résultats obtenus, l'outil permet d'intégrer et de visualiser conjointement et automatiquement ces analyses, en les présentant dans un tableau de bord interactif et dans des rapports générés aux formats HTML et Word.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La categorización del riesgo para cada uno de los componentes del análisis de sarampión y rubeola se encuentra %s. Para polio se encuentra %s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The risk categorization for each component of the measles and rubella analysis can be found %s. For polio, it can be found %s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A categorização do risco para cada um dos componentes da análise de sarampo e rubéola encontra-se %s. Para poliomielite, encontra-se %s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La catégorisation du risque pour chacune des composantes de l'analyse de la rougeole et de la rubéole se trouve %s. Pour la poliomyélite, elle se trouve %s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_about_link_word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ici</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visualización conjunta del riesgo de Polio, Sarampión y Rubéola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint Visualization of Polio, Measles, and Rubella Risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visualização conjunta do risco de poliomielite, sarampo e rubéola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visualisation conjointe du risque de poliomyélite, de rougeole et de rubéole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_synthesis_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Síntesis comparativa de la distribución del riesgo por componente para polio, sarampión y rubeola. %s, %s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparative synthesis of risk distribution by component for polio, measles, and rubella. %s, %s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Síntese comparativa da distribuição do risco por componente para poliomielite, sarampo e rubéola. %s, %s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synthèse comparative de la distribution du risque par composante pour la poliomyélite, la rougeole et la rubéole. %s, %s.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_synthesis_col_component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_synthesis_col_low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajo riesgo (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low risk (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baixo risco (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risque faible (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_synthesis_col_medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riesgo medio (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium risk (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risco médio (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risque moyen (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_synthesis_col_high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto riesgo (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High risk (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto risco (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risque élevé (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_synthesis_col_very_high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muy alto riesgo (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very high risk (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risco muito alto (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risque très élevé (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_synthesis_row_general</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil de risque général</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultados del riesgo conjunto por municipio para polio, sarampión y rubeola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint risk results by municipality for polio, measles, and rubella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultados do risco conjunto por município para poliomielite, sarampo e rubéola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résultats du risque conjoint par municipalité pour la poliomyélite, la rougeole et la rubéole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mapa de clasificación de riesgo para polio, sarampión y rubéola por municipio - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk classification map for polio, measles, and rubella by municipality - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mapa de classificação de risco para poliomielite, sarampo e rubéola por município - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carte de classification du risque pour la poliomyélite, la rougeole et la rubéole par municipalité - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribución de municipios para polio, sarampión y rubeola según categoría de riesgo - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution of municipalities for polio, measles, and rubella by risk category - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribuição de municípios para poliomielite, sarampo e rubéola segundo categoria de risco - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répartition des municipalités pour la poliomyélite, la rougeole et la rubéole selon la catégorie de risque - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_immunity_map_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribución espacial por categoría de riesgo e inmunidad poblacional para polio, sarampión y rubeola - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatial distribution by risk category and population immunity for polio, measles, and rubella - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribuição espacial por categoria de risco e imunidade populacional para poliomielite, sarampo e rubéola - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répartition spatiale par catégorie de risque et immunité de la population pour la poliomyélite, la rougeole et la rubéole - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_immunity_distribution_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribución de municipios para polio, sarampión y rubeola según categoría de riesgo e inmunidad poblacional - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution of municipalities for polio, measles, and rubella by risk category and population immunity - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribuição de municípios para poliomielite, sarampo e rubéola segundo categoria de risco e imunidade populacional - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répartition des municipalités pour la poliomyélite, la rougeole et la rubéole selon la catégorie de risque et l'immunité de la population - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_immunity_table_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultados del riesgo conjunto de inmunidad poblacional por municipio para polio, sarampión y rubeola - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint population immunity risk results by municipality for polio, measles, and rubella - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultados do risco conjunto de imunidade populacional por município para poliomielite, sarampo e rubéola - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résultats du risque conjoint d'immunité de la population par municipalité pour la poliomyélite, la rougeole et la rubéole - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_surveillance_map_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribución espacial por categoría de riesgo y calidad de la vigilancia para polio, sarampión y rubeola - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatial distribution by risk category and surveillance quality for polio, measles, and rubella - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribuição espacial por categoria de risco e qualidade da vigilância para poliomielite, sarampo e rubéola - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répartition spatiale par catégorie de risque et qualité de la surveillance pour la poliomyélite, la rougeole et la rubéole - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_surveillance_distribution_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribución de municipios para polio, sarampión y rubeola según categoría de riesgo y calidad de la vigilancia - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution of municipalities for polio, measles, and rubella by risk category and surveillance quality - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribuição de municípios para poliomielite, sarampo e rubéola segundo categoria de risco e qualidade da vigilância - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répartition des municipalités pour la poliomyélite, la rougeole et la rubéole selon la catégorie de risque et la qualité de la surveillance - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_surveillance_table_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultados del riesgo conjunto de calidad de la vigilancia por municipio para polio, sarampión y rubeola - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint surveillance quality risk results by municipality for polio, measles, and rubella - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultados do risco conjunto de qualidade da vigilância por município para poliomielite, sarampo e rubéola - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résultats du risque conjoint de qualité de la surveillance par municipalité pour la poliomyélite, la rougeole et la rubéole - %s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joint_barplot_xaxis_title</t>
   </si>
 </sst>
 </file>
@@ -16827,16 +17289,16 @@
         <v>2631</v>
       </c>
       <c r="B203" t="s">
-        <v>2632</v>
+        <v>2999</v>
       </c>
       <c r="C203" t="s">
-        <v>2633</v>
+        <v>3000</v>
       </c>
       <c r="D203" t="s">
-        <v>2634</v>
+        <v>3001</v>
       </c>
       <c r="E203" t="s">
-        <v>2635</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="204">
@@ -16844,16 +17306,16 @@
         <v>2636</v>
       </c>
       <c r="B204" t="s">
-        <v>2637</v>
+        <v>3032</v>
       </c>
       <c r="C204" t="s">
-        <v>2638</v>
+        <v>3033</v>
       </c>
       <c r="D204" t="s">
-        <v>2639</v>
+        <v>3034</v>
       </c>
       <c r="E204" t="s">
-        <v>2640</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="205">
@@ -16912,16 +17374,16 @@
         <v>2655</v>
       </c>
       <c r="B208" t="s">
-        <v>2656</v>
+        <v>3036</v>
       </c>
       <c r="C208" t="s">
-        <v>2657</v>
+        <v>3037</v>
       </c>
       <c r="D208" t="s">
-        <v>2658</v>
+        <v>3038</v>
       </c>
       <c r="E208" t="s">
-        <v>2659</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="209">
@@ -16929,16 +17391,16 @@
         <v>2660</v>
       </c>
       <c r="B209" t="s">
-        <v>2661</v>
+        <v>3040</v>
       </c>
       <c r="C209" t="s">
-        <v>2662</v>
+        <v>3041</v>
       </c>
       <c r="D209" t="s">
-        <v>2663</v>
+        <v>3042</v>
       </c>
       <c r="E209" t="s">
-        <v>2664</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="210">
@@ -17065,16 +17527,16 @@
         <v>2696</v>
       </c>
       <c r="B217" t="s">
-        <v>2697</v>
+        <v>2034</v>
       </c>
       <c r="C217" t="s">
-        <v>2698</v>
+        <v>2035</v>
       </c>
       <c r="D217" t="s">
-        <v>2699</v>
+        <v>2036</v>
       </c>
       <c r="E217" t="s">
-        <v>2700</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="218">
@@ -17198,733 +17660,1158 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>2729</v>
+        <v>2748</v>
       </c>
       <c r="B225" t="s">
-        <v>2730</v>
+        <v>2749</v>
       </c>
       <c r="C225" t="s">
-        <v>2731</v>
+        <v>2750</v>
       </c>
       <c r="D225" t="s">
-        <v>2730</v>
+        <v>2751</v>
       </c>
       <c r="E225" t="s">
-        <v>2732</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>2733</v>
+        <v>2753</v>
       </c>
       <c r="B226" t="s">
-        <v>2734</v>
+        <v>2754</v>
       </c>
       <c r="C226" t="s">
-        <v>2735</v>
+        <v>2755</v>
       </c>
       <c r="D226" t="s">
-        <v>2736</v>
+        <v>2756</v>
       </c>
       <c r="E226" t="s">
-        <v>2737</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>2738</v>
+        <v>2758</v>
       </c>
       <c r="B227" t="s">
-        <v>2739</v>
+        <v>2759</v>
       </c>
       <c r="C227" t="s">
-        <v>2740</v>
+        <v>2760</v>
       </c>
       <c r="D227" t="s">
-        <v>2741</v>
+        <v>2761</v>
       </c>
       <c r="E227" t="s">
-        <v>2742</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>2743</v>
+        <v>2763</v>
       </c>
       <c r="B228" t="s">
-        <v>2744</v>
+        <v>2764</v>
       </c>
       <c r="C228" t="s">
-        <v>2745</v>
+        <v>2765</v>
       </c>
       <c r="D228" t="s">
-        <v>2746</v>
+        <v>2766</v>
       </c>
       <c r="E228" t="s">
-        <v>2747</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>2748</v>
+        <v>2768</v>
       </c>
       <c r="B229" t="s">
-        <v>2749</v>
+        <v>2769</v>
       </c>
       <c r="C229" t="s">
-        <v>2750</v>
+        <v>2770</v>
       </c>
       <c r="D229" t="s">
-        <v>2751</v>
+        <v>2771</v>
       </c>
       <c r="E229" t="s">
-        <v>2752</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>2753</v>
+        <v>2773</v>
       </c>
       <c r="B230" t="s">
-        <v>2754</v>
+        <v>2774</v>
       </c>
       <c r="C230" t="s">
-        <v>2755</v>
+        <v>2775</v>
       </c>
       <c r="D230" t="s">
-        <v>2756</v>
+        <v>2776</v>
       </c>
       <c r="E230" t="s">
-        <v>2757</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>2758</v>
+        <v>2778</v>
       </c>
       <c r="B231" t="s">
-        <v>2759</v>
+        <v>2779</v>
       </c>
       <c r="C231" t="s">
-        <v>2760</v>
+        <v>2780</v>
       </c>
       <c r="D231" t="s">
-        <v>2761</v>
+        <v>2781</v>
       </c>
       <c r="E231" t="s">
-        <v>2762</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>2763</v>
+        <v>2783</v>
       </c>
       <c r="B232" t="s">
-        <v>2764</v>
+        <v>2784</v>
       </c>
       <c r="C232" t="s">
-        <v>2765</v>
+        <v>2785</v>
       </c>
       <c r="D232" t="s">
-        <v>2766</v>
+        <v>2786</v>
       </c>
       <c r="E232" t="s">
-        <v>2767</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>2768</v>
+        <v>2788</v>
       </c>
       <c r="B233" t="s">
-        <v>2769</v>
+        <v>2789</v>
       </c>
       <c r="C233" t="s">
-        <v>2770</v>
+        <v>2790</v>
       </c>
       <c r="D233" t="s">
-        <v>2771</v>
+        <v>2791</v>
       </c>
       <c r="E233" t="s">
-        <v>2772</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>2773</v>
+        <v>2793</v>
       </c>
       <c r="B234" t="s">
-        <v>2774</v>
+        <v>2794</v>
       </c>
       <c r="C234" t="s">
-        <v>2775</v>
+        <v>2795</v>
       </c>
       <c r="D234" t="s">
-        <v>2776</v>
+        <v>2796</v>
       </c>
       <c r="E234" t="s">
-        <v>2777</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>2778</v>
+        <v>2798</v>
       </c>
       <c r="B235" t="s">
-        <v>2779</v>
+        <v>2799</v>
       </c>
       <c r="C235" t="s">
-        <v>2780</v>
+        <v>2800</v>
       </c>
       <c r="D235" t="s">
-        <v>2781</v>
+        <v>2801</v>
       </c>
       <c r="E235" t="s">
-        <v>2782</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>2783</v>
+        <v>2803</v>
       </c>
       <c r="B236" t="s">
-        <v>2784</v>
+        <v>2804</v>
       </c>
       <c r="C236" t="s">
-        <v>2785</v>
+        <v>2805</v>
       </c>
       <c r="D236" t="s">
-        <v>2786</v>
+        <v>2806</v>
       </c>
       <c r="E236" t="s">
-        <v>2787</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>2788</v>
+        <v>2807</v>
       </c>
       <c r="B237" t="s">
-        <v>2789</v>
+        <v>2808</v>
       </c>
       <c r="C237" t="s">
-        <v>2790</v>
+        <v>2809</v>
       </c>
       <c r="D237" t="s">
-        <v>2791</v>
+        <v>2810</v>
       </c>
       <c r="E237" t="s">
-        <v>2792</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>2793</v>
+        <v>2812</v>
       </c>
       <c r="B238" t="s">
-        <v>2794</v>
+        <v>2813</v>
       </c>
       <c r="C238" t="s">
-        <v>2795</v>
+        <v>2814</v>
       </c>
       <c r="D238" t="s">
-        <v>2796</v>
+        <v>2815</v>
       </c>
       <c r="E238" t="s">
-        <v>2797</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>2798</v>
+        <v>2817</v>
       </c>
       <c r="B239" t="s">
-        <v>2799</v>
+        <v>2818</v>
       </c>
       <c r="C239" t="s">
-        <v>2800</v>
+        <v>2819</v>
       </c>
       <c r="D239" t="s">
-        <v>2801</v>
+        <v>2820</v>
       </c>
       <c r="E239" t="s">
-        <v>2802</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>2803</v>
+        <v>2822</v>
       </c>
       <c r="B240" t="s">
-        <v>2804</v>
+        <v>2185</v>
       </c>
       <c r="C240" t="s">
-        <v>2805</v>
+        <v>2186</v>
       </c>
       <c r="D240" t="s">
-        <v>2806</v>
+        <v>2185</v>
       </c>
       <c r="E240" t="s">
-        <v>2805</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>2807</v>
+        <v>2823</v>
       </c>
       <c r="B241" t="s">
-        <v>2808</v>
+        <v>1903</v>
       </c>
       <c r="C241" t="s">
-        <v>2809</v>
+        <v>1904</v>
       </c>
       <c r="D241" t="s">
-        <v>2810</v>
+        <v>1905</v>
       </c>
       <c r="E241" t="s">
-        <v>2811</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>2812</v>
+        <v>2824</v>
       </c>
       <c r="B242" t="s">
-        <v>2813</v>
+        <v>2825</v>
       </c>
       <c r="C242" t="s">
-        <v>2814</v>
+        <v>2826</v>
       </c>
       <c r="D242" t="s">
-        <v>2815</v>
+        <v>2827</v>
       </c>
       <c r="E242" t="s">
-        <v>2816</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>2817</v>
+        <v>2829</v>
       </c>
       <c r="B243" t="s">
-        <v>2818</v>
+        <v>2830</v>
       </c>
       <c r="C243" t="s">
-        <v>2819</v>
+        <v>2831</v>
       </c>
       <c r="D243" t="s">
-        <v>2820</v>
+        <v>2832</v>
       </c>
       <c r="E243" t="s">
-        <v>2821</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>2822</v>
+        <v>2834</v>
       </c>
       <c r="B244" t="s">
-        <v>2185</v>
+        <v>2858</v>
       </c>
       <c r="C244" t="s">
-        <v>2186</v>
+        <v>2859</v>
       </c>
       <c r="D244" t="s">
-        <v>2185</v>
+        <v>2860</v>
       </c>
       <c r="E244" t="s">
-        <v>2187</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>2823</v>
+        <v>2839</v>
       </c>
       <c r="B245" t="s">
-        <v>1903</v>
+        <v>1952</v>
       </c>
       <c r="C245" t="s">
-        <v>1904</v>
+        <v>1953</v>
       </c>
       <c r="D245" t="s">
-        <v>1905</v>
+        <v>1954</v>
       </c>
       <c r="E245" t="s">
-        <v>1906</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>2824</v>
+        <v>2841</v>
       </c>
       <c r="B246" t="s">
-        <v>2825</v>
+        <v>2842</v>
       </c>
       <c r="C246" t="s">
-        <v>2826</v>
+        <v>1958</v>
       </c>
       <c r="D246" t="s">
-        <v>2827</v>
+        <v>1959</v>
       </c>
       <c r="E246" t="s">
-        <v>2828</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>2829</v>
+        <v>2843</v>
       </c>
       <c r="B247" t="s">
-        <v>2830</v>
+        <v>1962</v>
       </c>
       <c r="C247" t="s">
-        <v>2831</v>
+        <v>1963</v>
       </c>
       <c r="D247" t="s">
-        <v>2832</v>
+        <v>1964</v>
       </c>
       <c r="E247" t="s">
-        <v>2833</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>2834</v>
+        <v>2844</v>
       </c>
       <c r="B248" t="s">
-        <v>2858</v>
+        <v>2845</v>
       </c>
       <c r="C248" t="s">
-        <v>2859</v>
+        <v>1968</v>
       </c>
       <c r="D248" t="s">
-        <v>2860</v>
+        <v>1969</v>
       </c>
       <c r="E248" t="s">
-        <v>2861</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>2839</v>
+        <v>2846</v>
       </c>
       <c r="B249" t="s">
-        <v>1952</v>
+        <v>2847</v>
       </c>
       <c r="C249" t="s">
-        <v>1953</v>
+        <v>2847</v>
       </c>
       <c r="D249" t="s">
-        <v>1954</v>
+        <v>2847</v>
       </c>
       <c r="E249" t="s">
-        <v>2840</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>2841</v>
+        <v>2848</v>
       </c>
       <c r="B250" t="s">
-        <v>2842</v>
+        <v>2849</v>
       </c>
       <c r="C250" t="s">
-        <v>1958</v>
+        <v>2850</v>
       </c>
       <c r="D250" t="s">
-        <v>1959</v>
+        <v>2851</v>
       </c>
       <c r="E250" t="s">
-        <v>1960</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>2843</v>
+        <v>2853</v>
       </c>
       <c r="B251" t="s">
-        <v>1962</v>
+        <v>2854</v>
       </c>
       <c r="C251" t="s">
-        <v>1963</v>
+        <v>2855</v>
       </c>
       <c r="D251" t="s">
-        <v>1964</v>
+        <v>2856</v>
       </c>
       <c r="E251" t="s">
-        <v>1965</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>2844</v>
+        <v>2862</v>
       </c>
       <c r="B252" t="s">
-        <v>2845</v>
+        <v>1977</v>
       </c>
       <c r="C252" t="s">
-        <v>1968</v>
+        <v>1976</v>
       </c>
       <c r="D252" t="s">
-        <v>1969</v>
+        <v>1978</v>
       </c>
       <c r="E252" t="s">
-        <v>1970</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>2846</v>
+        <v>2868</v>
       </c>
       <c r="B253" t="s">
-        <v>2847</v>
+        <v>2869</v>
       </c>
       <c r="C253" t="s">
-        <v>2847</v>
+        <v>2870</v>
       </c>
       <c r="D253" t="s">
-        <v>2847</v>
+        <v>2871</v>
       </c>
       <c r="E253" t="s">
-        <v>2847</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>2848</v>
+        <v>2873</v>
       </c>
       <c r="B254" t="s">
-        <v>2849</v>
+        <v>2874</v>
       </c>
       <c r="C254" t="s">
-        <v>2850</v>
+        <v>2875</v>
       </c>
       <c r="D254" t="s">
-        <v>2851</v>
+        <v>2874</v>
       </c>
       <c r="E254" t="s">
-        <v>2852</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>2853</v>
+        <v>2876</v>
       </c>
       <c r="B255" t="s">
-        <v>2854</v>
+        <v>2877</v>
       </c>
       <c r="C255" t="s">
-        <v>2855</v>
+        <v>2878</v>
       </c>
       <c r="D255" t="s">
-        <v>2856</v>
+        <v>2879</v>
       </c>
       <c r="E255" t="s">
-        <v>2857</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>2862</v>
+        <v>2881</v>
       </c>
       <c r="B256" t="s">
-        <v>1977</v>
+        <v>2882</v>
       </c>
       <c r="C256" t="s">
-        <v>1976</v>
+        <v>2883</v>
       </c>
       <c r="D256" t="s">
-        <v>1978</v>
+        <v>2884</v>
       </c>
       <c r="E256" t="s">
-        <v>2867</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>2868</v>
+        <v>2886</v>
       </c>
       <c r="B257" t="s">
-        <v>2869</v>
+        <v>2887</v>
       </c>
       <c r="C257" t="s">
-        <v>2870</v>
+        <v>2888</v>
       </c>
       <c r="D257" t="s">
-        <v>2871</v>
+        <v>2889</v>
       </c>
       <c r="E257" t="s">
-        <v>2872</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>2873</v>
+        <v>2891</v>
       </c>
       <c r="B258" t="s">
-        <v>2874</v>
+        <v>2892</v>
       </c>
       <c r="C258" t="s">
-        <v>2875</v>
+        <v>2893</v>
       </c>
       <c r="D258" t="s">
-        <v>2874</v>
+        <v>2894</v>
       </c>
       <c r="E258" t="s">
-        <v>2875</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>2876</v>
+        <v>2896</v>
       </c>
       <c r="B259" t="s">
-        <v>2877</v>
+        <v>2897</v>
       </c>
       <c r="C259" t="s">
-        <v>2878</v>
+        <v>2898</v>
       </c>
       <c r="D259" t="s">
-        <v>2879</v>
+        <v>2899</v>
       </c>
       <c r="E259" t="s">
-        <v>2880</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>2881</v>
+        <v>2901</v>
       </c>
       <c r="B260" t="s">
-        <v>2882</v>
+        <v>2902</v>
       </c>
       <c r="C260" t="s">
-        <v>2883</v>
+        <v>2903</v>
       </c>
       <c r="D260" t="s">
-        <v>2884</v>
+        <v>2904</v>
       </c>
       <c r="E260" t="s">
-        <v>2885</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>2886</v>
+        <v>2906</v>
       </c>
       <c r="B261" t="s">
-        <v>2887</v>
+        <v>2907</v>
       </c>
       <c r="C261" t="s">
-        <v>2888</v>
+        <v>2908</v>
       </c>
       <c r="D261" t="s">
-        <v>2889</v>
+        <v>2909</v>
       </c>
       <c r="E261" t="s">
-        <v>2890</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>2891</v>
+        <v>2911</v>
       </c>
       <c r="B262" t="s">
-        <v>2892</v>
+        <v>2912</v>
       </c>
       <c r="C262" t="s">
-        <v>2893</v>
+        <v>2913</v>
       </c>
       <c r="D262" t="s">
-        <v>2894</v>
+        <v>2914</v>
       </c>
       <c r="E262" t="s">
-        <v>2895</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>2896</v>
+        <v>2916</v>
       </c>
       <c r="B263" t="s">
-        <v>2897</v>
+        <v>2917</v>
       </c>
       <c r="C263" t="s">
-        <v>2898</v>
+        <v>2918</v>
       </c>
       <c r="D263" t="s">
-        <v>2899</v>
+        <v>2919</v>
       </c>
       <c r="E263" t="s">
-        <v>2900</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>2901</v>
+        <v>2921</v>
       </c>
       <c r="B264" t="s">
-        <v>2902</v>
+        <v>2922</v>
       </c>
       <c r="C264" t="s">
-        <v>2903</v>
+        <v>2923</v>
       </c>
       <c r="D264" t="s">
-        <v>2904</v>
+        <v>2924</v>
       </c>
       <c r="E264" t="s">
-        <v>2905</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>2906</v>
+        <v>2928</v>
       </c>
       <c r="B265" t="s">
-        <v>2907</v>
+        <v>2929</v>
       </c>
       <c r="C265" t="s">
-        <v>2908</v>
+        <v>2930</v>
       </c>
       <c r="D265" t="s">
-        <v>2909</v>
+        <v>2931</v>
       </c>
       <c r="E265" t="s">
-        <v>2910</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>2911</v>
+        <v>2933</v>
       </c>
       <c r="B266" t="s">
-        <v>2912</v>
+        <v>2934</v>
       </c>
       <c r="C266" t="s">
-        <v>2913</v>
+        <v>2935</v>
       </c>
       <c r="D266" t="s">
-        <v>2914</v>
+        <v>2936</v>
       </c>
       <c r="E266" t="s">
-        <v>2915</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>2916</v>
+        <v>2938</v>
       </c>
       <c r="B267" t="s">
-        <v>2917</v>
+        <v>2939</v>
       </c>
       <c r="C267" t="s">
-        <v>2918</v>
+        <v>2940</v>
       </c>
       <c r="D267" t="s">
-        <v>2919</v>
+        <v>2941</v>
       </c>
       <c r="E267" t="s">
-        <v>2920</v>
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>2943</v>
+      </c>
+      <c r="B268" t="s">
+        <v>2944</v>
+      </c>
+      <c r="C268" t="s">
+        <v>2945</v>
+      </c>
+      <c r="D268" t="s">
+        <v>2946</v>
+      </c>
+      <c r="E268" t="s">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B269" t="s">
+        <v>2949</v>
+      </c>
+      <c r="C269" t="s">
+        <v>2950</v>
+      </c>
+      <c r="D269" t="s">
+        <v>2951</v>
+      </c>
+      <c r="E269" t="s">
+        <v>2952</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B270" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C270" t="s">
+        <v>2809</v>
+      </c>
+      <c r="D270" t="s">
+        <v>2959</v>
+      </c>
+      <c r="E270" t="s">
+        <v>2811</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>2960</v>
+      </c>
+      <c r="B271" t="s">
+        <v>2961</v>
+      </c>
+      <c r="C271" t="s">
+        <v>2962</v>
+      </c>
+      <c r="D271" t="s">
+        <v>2963</v>
+      </c>
+      <c r="E271" t="s">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>2965</v>
+      </c>
+      <c r="B272" t="s">
+        <v>2966</v>
+      </c>
+      <c r="C272" t="s">
+        <v>2967</v>
+      </c>
+      <c r="D272" t="s">
+        <v>2968</v>
+      </c>
+      <c r="E272" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B273" t="s">
+        <v>2971</v>
+      </c>
+      <c r="C273" t="s">
+        <v>2972</v>
+      </c>
+      <c r="D273" t="s">
+        <v>2973</v>
+      </c>
+      <c r="E273" t="s">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>2975</v>
+      </c>
+      <c r="B274" t="s">
+        <v>2976</v>
+      </c>
+      <c r="C274" t="s">
+        <v>2977</v>
+      </c>
+      <c r="D274" t="s">
+        <v>2978</v>
+      </c>
+      <c r="E274" t="s">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>2980</v>
+      </c>
+      <c r="B275" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C275" t="s">
+        <v>2982</v>
+      </c>
+      <c r="D275" t="s">
+        <v>2983</v>
+      </c>
+      <c r="E275" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>2985</v>
+      </c>
+      <c r="B276" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C276" t="s">
+        <v>2987</v>
+      </c>
+      <c r="D276" t="s">
+        <v>2988</v>
+      </c>
+      <c r="E276" t="s">
+        <v>2989</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>2953</v>
+      </c>
+      <c r="B277" t="s">
+        <v>2990</v>
+      </c>
+      <c r="C277" t="s">
+        <v>2991</v>
+      </c>
+      <c r="D277" t="s">
+        <v>2992</v>
+      </c>
+      <c r="E277" t="s">
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>2994</v>
+      </c>
+      <c r="B278" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C278" t="s">
+        <v>2996</v>
+      </c>
+      <c r="D278" t="s">
+        <v>2997</v>
+      </c>
+      <c r="E278" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>3003</v>
+      </c>
+      <c r="B279" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C279" t="s">
+        <v>3005</v>
+      </c>
+      <c r="D279" t="s">
+        <v>3006</v>
+      </c>
+      <c r="E279" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>3008</v>
+      </c>
+      <c r="B280" t="s">
+        <v>2647</v>
+      </c>
+      <c r="C280" t="s">
+        <v>2648</v>
+      </c>
+      <c r="D280" t="s">
+        <v>2647</v>
+      </c>
+      <c r="E280" t="s">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B281" t="s">
+        <v>3011</v>
+      </c>
+      <c r="C281" t="s">
+        <v>3012</v>
+      </c>
+      <c r="D281" t="s">
+        <v>3013</v>
+      </c>
+      <c r="E281" t="s">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>3015</v>
+      </c>
+      <c r="B282" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C282" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D282" t="s">
+        <v>3018</v>
+      </c>
+      <c r="E282" t="s">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B283" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C283" t="s">
+        <v>3022</v>
+      </c>
+      <c r="D283" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E283" t="s">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>3025</v>
+      </c>
+      <c r="B284" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C284" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D284" t="s">
+        <v>3028</v>
+      </c>
+      <c r="E284" t="s">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>3030</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C285" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E285" t="s">
+        <v>3031</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B286" t="s">
+        <v>3045</v>
+      </c>
+      <c r="C286" t="s">
+        <v>3046</v>
+      </c>
+      <c r="D286" t="s">
+        <v>3047</v>
+      </c>
+      <c r="E286" t="s">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B287" t="s">
+        <v>3050</v>
+      </c>
+      <c r="C287" t="s">
+        <v>3051</v>
+      </c>
+      <c r="D287" t="s">
+        <v>3052</v>
+      </c>
+      <c r="E287" t="s">
+        <v>3053</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B288" t="s">
+        <v>3055</v>
+      </c>
+      <c r="C288" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D288" t="s">
+        <v>3057</v>
+      </c>
+      <c r="E288" t="s">
+        <v>3058</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B289" t="s">
+        <v>3060</v>
+      </c>
+      <c r="C289" t="s">
+        <v>3061</v>
+      </c>
+      <c r="D289" t="s">
+        <v>3062</v>
+      </c>
+      <c r="E289" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B290" t="s">
+        <v>3065</v>
+      </c>
+      <c r="C290" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D290" t="s">
+        <v>3067</v>
+      </c>
+      <c r="E290" t="s">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>3069</v>
+      </c>
+      <c r="B291" t="s">
+        <v>3070</v>
+      </c>
+      <c r="C291" t="s">
+        <v>3071</v>
+      </c>
+      <c r="D291" t="s">
+        <v>3072</v>
+      </c>
+      <c r="E291" t="s">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>3074</v>
+      </c>
+      <c r="B292" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C292" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D292" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E292" t="s">
+        <v>1988</v>
       </c>
     </row>
   </sheetData>
